--- a/src/doc/calendario.xlsx
+++ b/src/doc/calendario.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C144F3F5-65B1-4C13-83AA-DC4951F3D5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F4A58A-B354-4621-BDCB-B76FBB237B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="453">
   <si>
     <t>Domingo 1º de Adviento</t>
   </si>
@@ -1335,18 +1336,130 @@
   <si>
     <t>Mateo 15, 21-28</t>
   </si>
+  <si>
+    <t>Samuel 1, 1-8</t>
+  </si>
+  <si>
+    <t>Salmo 115, 12-13. 14 y 17. 18-19</t>
+  </si>
+  <si>
+    <t>Mc 1, 15</t>
+  </si>
+  <si>
+    <t>Marcos 1, 14-20</t>
+  </si>
+  <si>
+    <t>martes</t>
+  </si>
+  <si>
+    <t>Samuel 1, 9-20</t>
+  </si>
+  <si>
+    <t>1Samuel 2, 1. 4-5. 6-7. 8</t>
+  </si>
+  <si>
+    <t>1Ts 2, 13</t>
+  </si>
+  <si>
+    <t>Marcos 1, 21-28</t>
+  </si>
+  <si>
+    <t>TO-s1-PAR</t>
+  </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
+    <t>Miercoles</t>
+  </si>
+  <si>
+    <t>Jueves</t>
+  </si>
+  <si>
+    <t>Viernes</t>
+  </si>
+  <si>
+    <t>Sabado</t>
+  </si>
+  <si>
+    <t>TO-s2-PAR</t>
+  </si>
+  <si>
+    <t>1 Samuel 3, 1-10. 19-20</t>
+  </si>
+  <si>
+    <t>Salmo 39, 2 y 5. 7-8a. 8b-9. 10</t>
+  </si>
+  <si>
+    <t>Jn 10, 27</t>
+  </si>
+  <si>
+    <t>san Marcos 1, 29-39</t>
+  </si>
+  <si>
+    <t>1 Samuel 4, 1-11</t>
+  </si>
+  <si>
+    <t>Salmo 43, 10-11. 14-15. 24-25</t>
+  </si>
+  <si>
+    <t>Mt 4, 23</t>
+  </si>
+  <si>
+    <t>san Marcos 1, 40-45</t>
+  </si>
+  <si>
+    <t>1 Samuel 8, 4-7. 10-22a</t>
+  </si>
+  <si>
+    <t>Salmo 88, 16-17. 18-19</t>
+  </si>
+  <si>
+    <t>Lc 7, 16</t>
+  </si>
+  <si>
+    <t>Marcos 2, 1-12</t>
+  </si>
+  <si>
+    <t>1 Samuel 9, 1-4. 17-19; 10, 1a</t>
+  </si>
+  <si>
+    <t>Salmo 20, 2-3. 4-5. 6-7</t>
+  </si>
+  <si>
+    <t>Marcos 2, 13-17</t>
+  </si>
+  <si>
+    <t>1 Samuel 1, 1-8</t>
+  </si>
+  <si>
+    <t>1 Samuel 1, 9-20</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFFF0000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1369,8 +1482,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1706,20 +1824,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10C50CC-0950-4C80-A067-6CCB3F4EAE54}">
   <dimension ref="A1:L114"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" customWidth="1"/>
-    <col min="9" max="10" width="33.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1796875" customWidth="1"/>
+    <col min="9" max="10" width="33.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -1742,7 +1860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1769,7 +1887,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1796,7 +1914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1823,7 +1941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1850,7 +1968,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1880,7 +1998,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1900,14 +2018,14 @@
         <v>44</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" ref="G7:G70" si="1">IF(J7="",I7,_xlfn.CONCAT(I7," / ",J7))</f>
+        <f t="shared" ref="G7:G69" si="1">IF(J7="",I7,_xlfn.CONCAT(I7," / ",J7))</f>
         <v>Lucas 2, 1-14</v>
       </c>
       <c r="I7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1934,7 +2052,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1964,7 +2082,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1991,7 +2109,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -2018,7 +2136,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -2048,7 +2166,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -2075,7 +2193,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2102,7 +2220,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2129,7 +2247,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -2156,7 +2274,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2186,7 +2304,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -2216,7 +2334,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -2246,7 +2364,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2273,7 +2391,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2300,7 +2418,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -2327,7 +2445,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2342,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2369,7 +2487,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -2396,7 +2514,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2423,7 +2541,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -2450,7 +2568,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -2477,7 +2595,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -2504,7 +2622,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2531,7 +2649,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2558,7 +2676,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2585,7 +2703,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2612,7 +2730,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -2639,7 +2757,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -2669,7 +2787,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -2699,7 +2817,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -2726,7 +2844,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -2756,7 +2874,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -2783,7 +2901,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -2810,7 +2928,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>31</v>
       </c>
@@ -2840,7 +2958,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>31</v>
       </c>
@@ -2867,7 +2985,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>31</v>
       </c>
@@ -2894,7 +3012,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>31</v>
       </c>
@@ -2921,7 +3039,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>31</v>
       </c>
@@ -2948,7 +3066,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>31</v>
       </c>
@@ -2975,7 +3093,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>31</v>
       </c>
@@ -3002,7 +3120,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>31</v>
       </c>
@@ -3029,7 +3147,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>31</v>
       </c>
@@ -3056,7 +3174,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>31</v>
       </c>
@@ -3086,7 +3204,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -3116,7 +3234,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>31</v>
       </c>
@@ -3146,7 +3264,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>31</v>
       </c>
@@ -3173,7 +3291,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>31</v>
       </c>
@@ -3200,7 +3318,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>31</v>
       </c>
@@ -3227,7 +3345,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -3254,7 +3372,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>31</v>
       </c>
@@ -3281,7 +3399,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>31</v>
       </c>
@@ -3308,7 +3426,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>31</v>
       </c>
@@ -3335,7 +3453,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>31</v>
       </c>
@@ -3362,7 +3480,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>31</v>
       </c>
@@ -3389,7 +3507,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -3416,7 +3534,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>31</v>
       </c>
@@ -3446,7 +3564,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>31</v>
       </c>
@@ -3473,7 +3591,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>31</v>
       </c>
@@ -3500,7 +3618,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>31</v>
       </c>
@@ -3527,7 +3645,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>31</v>
       </c>
@@ -3554,7 +3672,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>31</v>
       </c>
@@ -3584,7 +3702,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>31</v>
       </c>
@@ -3611,273 +3729,603 @@
         <v>418</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G70">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G71">
-        <f t="shared" ref="G71:G114" si="2">IF(J71="",I71,_xlfn.CONCAT(I71," / ",J71))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G72">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G74">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>429</v>
+      </c>
+      <c r="B70" t="s">
+        <v>430</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>429</v>
+      </c>
+      <c r="B71" t="s">
+        <v>424</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D71" t="s">
+        <v>426</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>429</v>
+      </c>
+      <c r="B72" t="s">
+        <v>431</v>
+      </c>
+      <c r="C72" t="s">
+        <v>436</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>429</v>
+      </c>
+      <c r="B73" t="s">
+        <v>432</v>
+      </c>
+      <c r="C73" t="s">
+        <v>440</v>
+      </c>
+      <c r="D73" t="s">
+        <v>441</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>429</v>
+      </c>
+      <c r="B74" t="s">
+        <v>433</v>
+      </c>
+      <c r="C74" t="s">
+        <v>444</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>429</v>
+      </c>
+      <c r="B75" t="s">
+        <v>434</v>
+      </c>
+      <c r="C75" t="s">
+        <v>448</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>435</v>
+      </c>
+      <c r="B76" t="s">
+        <v>430</v>
+      </c>
       <c r="G76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" ref="G76:G114" si="2">IF(J76="",I76,_xlfn.CONCAT(I76," / ",J76))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>435</v>
+      </c>
+      <c r="B77" t="s">
+        <v>424</v>
+      </c>
       <c r="G77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>435</v>
+      </c>
+      <c r="B78" t="s">
+        <v>431</v>
+      </c>
       <c r="G78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>435</v>
+      </c>
+      <c r="B79" t="s">
+        <v>432</v>
+      </c>
       <c r="G79">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>435</v>
+      </c>
+      <c r="B80" t="s">
+        <v>433</v>
+      </c>
       <c r="G80">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>435</v>
+      </c>
+      <c r="B81" t="s">
+        <v>434</v>
+      </c>
       <c r="G81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G82">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G83">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G84">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G86">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G88">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G91">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G92">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G93">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G95">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G98">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G99">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G100">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G102">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G103">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G105">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G108">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G109">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G110">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G112">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G114">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AFBACE-E0D0-47E0-A7DB-4F0CC57B5A5B}">
+  <dimension ref="A2:G13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E4" t="s">
+        <v>438</v>
+      </c>
+      <c r="F4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D5" t="s">
+        <v>441</v>
+      </c>
+      <c r="E5" t="s">
+        <v>442</v>
+      </c>
+      <c r="F5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E6" t="s">
+        <v>446</v>
+      </c>
+      <c r="F6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D7" t="s">
+        <v>449</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>435</v>
+      </c>
+      <c r="B8" t="s">
+        <v>430</v>
+      </c>
+      <c r="G8">
+        <f t="shared" ref="G8:G13" si="0">IF(J8="",I8,_xlfn.CONCAT(I8," / ",J8))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>424</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" t="s">
+        <v>431</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>435</v>
+      </c>
+      <c r="B11" t="s">
+        <v>432</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" t="s">
+        <v>433</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B13" t="s">
+        <v>434</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/src/doc/calendario.xlsx
+++ b/src/doc/calendario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F4A58A-B354-4621-BDCB-B76FBB237B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC8272D-78A6-40E5-8582-C7CA2013FBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
+    <workbookView xWindow="38280" yWindow="2205" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="825">
   <si>
     <t>Domingo 1º de Adviento</t>
   </si>
@@ -1435,12 +1435,1128 @@
   <si>
     <t>1 Samuel 1, 9-20</t>
   </si>
+  <si>
+    <t>1 Samuel 15, 16-23</t>
+  </si>
+  <si>
+    <t>Salmo 49, 8-9. 16bc-17. 21 y 23</t>
+  </si>
+  <si>
+    <t>Hb 4, 12</t>
+  </si>
+  <si>
+    <t>Marcos 2, 18-22</t>
+  </si>
+  <si>
+    <t>1 Samuel 16, 1-13</t>
+  </si>
+  <si>
+    <t>Salmo 88, 20. 21-22. 27-28</t>
+  </si>
+  <si>
+    <t>Ef 1, 17-18</t>
+  </si>
+  <si>
+    <t>Marcos 2, 23-28</t>
+  </si>
+  <si>
+    <t>1 Samuel 17, 32-33. 37. 40-51</t>
+  </si>
+  <si>
+    <t>Salmo 143, 1. 2. 9-10</t>
+  </si>
+  <si>
+    <t>Marcos 3, 1-6</t>
+  </si>
+  <si>
+    <t>1 Samuel 18, 6-9; 19, 1-7</t>
+  </si>
+  <si>
+    <t>Salmo 55, 2-3. 9-10. 11-12. 13</t>
+  </si>
+  <si>
+    <t>2Tm 1, 10</t>
+  </si>
+  <si>
+    <t>Marcos 3, 7-12</t>
+  </si>
+  <si>
+    <t>1 Samuel 24, 3-21</t>
+  </si>
+  <si>
+    <t>Salmo 56, 2. 3-4. 6 y 11</t>
+  </si>
+  <si>
+    <t>2Co 5, 19</t>
+  </si>
+  <si>
+    <t>Marcos 3, 13-19</t>
+  </si>
+  <si>
+    <t>1 Samuel 1, 1-4. 11-12. 19. 23-27</t>
+  </si>
+  <si>
+    <t>Salmo 79, 2-3. 5-7</t>
+  </si>
+  <si>
+    <t>Hch 16, 14</t>
+  </si>
+  <si>
+    <t>Marcos 3, 20-21</t>
+  </si>
+  <si>
+    <t>2 Samuel 5, 1-7. 10</t>
+  </si>
+  <si>
+    <t>Salmo 88, 20. 21-22. 25-26</t>
+  </si>
+  <si>
+    <t>Marcos 3, 22-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmo 23, 7. 8. 9. 10 </t>
+  </si>
+  <si>
+    <t>2 Samuel 6, 12b-15. 17-19</t>
+  </si>
+  <si>
+    <t>Mt 11, 25</t>
+  </si>
+  <si>
+    <t>Marcos 3, 31-35</t>
+  </si>
+  <si>
+    <t>2 Samuel 7, 4-17</t>
+  </si>
+  <si>
+    <t>Salmo 88, 4-5. 27-28. 29-30</t>
+  </si>
+  <si>
+    <t>Marcos 4, 1-20</t>
+  </si>
+  <si>
+    <t>2 Samuel 7, 18-19. 24-29</t>
+  </si>
+  <si>
+    <t>Salmo 131, 1-2. 3-5. 11. 12. 13-14</t>
+  </si>
+  <si>
+    <t>Sal 118, 105</t>
+  </si>
+  <si>
+    <t>Marcos 4, 21-25</t>
+  </si>
+  <si>
+    <t>2 Samuel 11, 1-4a. 5-10a. 13-17</t>
+  </si>
+  <si>
+    <t>Salmo 50, 3-4. 5-6a. 6bc-7. 10-11</t>
+  </si>
+  <si>
+    <t>Marcos 4, 26-34</t>
+  </si>
+  <si>
+    <t>2 Samuel 12, 1-7a. 10-17</t>
+  </si>
+  <si>
+    <t>Salmo 50 12-13. 14-15. 16-17</t>
+  </si>
+  <si>
+    <t>Jn 3, 16</t>
+  </si>
+  <si>
+    <t>Marcos 4, 35-41</t>
+  </si>
+  <si>
+    <t>2 Samuel 15, 13-14. 30; 16, 5-13</t>
+  </si>
+  <si>
+    <t>Salmo 3, 2-3, 4-5. 6-7</t>
+  </si>
+  <si>
+    <t>Marcos 5, 1-20</t>
+  </si>
+  <si>
+    <t>2 Samuel 18, 9-10. 14b. 24-25a. 30—19, 3</t>
+  </si>
+  <si>
+    <t>Salmo 85, 1-2. 3-4. 5-6</t>
+  </si>
+  <si>
+    <t>Mt 8, 17</t>
+  </si>
+  <si>
+    <t>Marcos 5, 21-43</t>
+  </si>
+  <si>
+    <t>2 Samuel 24, 2. 9-17</t>
+  </si>
+  <si>
+    <t>Salmo 31, 1-2. 5. 6. 7 </t>
+  </si>
+  <si>
+    <t>Marcos 6, 1-6</t>
+  </si>
+  <si>
+    <t>1 Reyes 2, 1-4. 10-12</t>
+  </si>
+  <si>
+    <t>1Crónicas 29, 10. 11ab. 11d-12a. 12</t>
+  </si>
+  <si>
+    <t>Marcos 6, 7-13</t>
+  </si>
+  <si>
+    <t>Sirácida 47, 2-13</t>
+  </si>
+  <si>
+    <t>Salmo 17, 31. 47 y 50. 51</t>
+  </si>
+  <si>
+    <t>Lc 8, 15</t>
+  </si>
+  <si>
+    <t>Marcos 6, 14-29</t>
+  </si>
+  <si>
+    <t>Salmo 118, 9. 10. 11. 12. 13. 14</t>
+  </si>
+  <si>
+    <t>1 Reyes 3, 4-13</t>
+  </si>
+  <si>
+    <t>Marcos 6, 30-34</t>
+  </si>
+  <si>
+    <t>1 Reyes 8, 1-7. 9-13</t>
+  </si>
+  <si>
+    <t>Salmo 131, 6-7. 8-10</t>
+  </si>
+  <si>
+    <t>Marcos 6, 53-56</t>
+  </si>
+  <si>
+    <t>1 Reyes 8, 22-23. 27-30</t>
+  </si>
+  <si>
+    <t>Salmo 83, 3. 4. 5 y 10. 11</t>
+  </si>
+  <si>
+    <t>Sal 118, 36a. 29b</t>
+  </si>
+  <si>
+    <t>Marcos 7, 1-13</t>
+  </si>
+  <si>
+    <t>1 Reyes 10, 1-10</t>
+  </si>
+  <si>
+    <t>Salmo 36, 5-6. 30-31. 39-40</t>
+  </si>
+  <si>
+    <t>Jn 17, 17</t>
+  </si>
+  <si>
+    <t>Marcos 7, 14-23</t>
+  </si>
+  <si>
+    <t>1 Reyes 11 ,4-13</t>
+  </si>
+  <si>
+    <t>Salmo 105, 3-4. 35-36. 37 y 40 </t>
+  </si>
+  <si>
+    <t>St 1, 21</t>
+  </si>
+  <si>
+    <t>Marcos 7, 24-30</t>
+  </si>
+  <si>
+    <t>1 Reyes 11, 29-32; 12, 19</t>
+  </si>
+  <si>
+    <t>Salmo 80, 10-11ab. 12-13. 14-15</t>
+  </si>
+  <si>
+    <t>Marcos 7, 31-37</t>
+  </si>
+  <si>
+    <t>1 Reyes 12, 26-32; 13, 33-34</t>
+  </si>
+  <si>
+    <t>Salmo 105, 6-7a. 19-20. 21-22</t>
+  </si>
+  <si>
+    <t>Mt 4, 4b</t>
+  </si>
+  <si>
+    <t>Marcos 8, 1-10</t>
+  </si>
+  <si>
+    <t>Santiago 1, 1-11</t>
+  </si>
+  <si>
+    <t>Salmo 118, 67. 68. 71. 72. 75. 76</t>
+  </si>
+  <si>
+    <t>Marcos 8, 11-13</t>
+  </si>
+  <si>
+    <t>Santiago 1, 12-18</t>
+  </si>
+  <si>
+    <t>Salmo 93, 12-13a. 14-15. 18-19 </t>
+  </si>
+  <si>
+    <t>Marcos 8, 14-21</t>
+  </si>
+  <si>
+    <t>Santiago 1, 19-27</t>
+  </si>
+  <si>
+    <t>Salmo 14, 2-3ab. 3cd-4ab. 5 </t>
+  </si>
+  <si>
+    <t>Marcos 8, 22-26</t>
+  </si>
+  <si>
+    <t>Santiago 2, 1-9</t>
+  </si>
+  <si>
+    <t>Salmo 33, 2-3. 4-5. 6-7</t>
+  </si>
+  <si>
+    <t>Jn 6, 63c. 68c</t>
+  </si>
+  <si>
+    <t>Marcos 8, 27-33</t>
+  </si>
+  <si>
+    <t>Santiago 2, 14-24. 26</t>
+  </si>
+  <si>
+    <t>Salmo 111, 1-2. 3-4. 5-6</t>
+  </si>
+  <si>
+    <t>Jn 15, 15b</t>
+  </si>
+  <si>
+    <t>Marcos 8, 34 - 9, 1</t>
+  </si>
+  <si>
+    <t>Santiago 3, 1-10</t>
+  </si>
+  <si>
+    <t>Salmo 11, 2-3. 4-5. 7-8 </t>
+  </si>
+  <si>
+    <t>san Marcos 9, 2-13</t>
+  </si>
+  <si>
+    <t>Santiago 3, 13-18</t>
+  </si>
+  <si>
+    <t>Salmo 18, 8. 9. 10. 15</t>
+  </si>
+  <si>
+    <t>Marcos 9, 14-29</t>
+  </si>
+  <si>
+    <t>Santiago 4, 1-10</t>
+  </si>
+  <si>
+    <t>Salmo 54, 7-8. 9-10a. 10b-11a. 23</t>
+  </si>
+  <si>
+    <t>Ga 6, 14</t>
+  </si>
+  <si>
+    <t>Marcos 9, 30-37</t>
+  </si>
+  <si>
+    <t>Santiago 4, 13-17</t>
+  </si>
+  <si>
+    <t>Salmo 48, 2-3. 6-7. 8-10. 11</t>
+  </si>
+  <si>
+    <t>Marcos 9, 38-40</t>
+  </si>
+  <si>
+    <t>Santiago 5, 1-6</t>
+  </si>
+  <si>
+    <t>Salmo 48, 14-15ab. 15cd-16. 17-18. 19-20</t>
+  </si>
+  <si>
+    <t>Marcos 9, 41-50</t>
+  </si>
+  <si>
+    <t>Santiago 5, 9-12</t>
+  </si>
+  <si>
+    <t>Salmo 102, 1-2. 3-4. 8-9. 11-12</t>
+  </si>
+  <si>
+    <t>Marcos 10, 1-12</t>
+  </si>
+  <si>
+    <t>Santiago 5, 13-20</t>
+  </si>
+  <si>
+    <t>Salmo 140, 1-2. 3 y 8 </t>
+  </si>
+  <si>
+    <t>Marcos 10, 13-16</t>
+  </si>
+  <si>
+    <t>1 Pedro 1, 3-9</t>
+  </si>
+  <si>
+    <t>Salmo 110, 1-2. 5-6. 9 y 10c</t>
+  </si>
+  <si>
+    <t>2Co 8, 9</t>
+  </si>
+  <si>
+    <t>Marcos 10, 17-27</t>
+  </si>
+  <si>
+    <t>1 Pedro 1, 10-16</t>
+  </si>
+  <si>
+    <t>Salmo 97, 1. 2-3ab. 3c-4</t>
+  </si>
+  <si>
+    <t>Marcos 10, 28-31</t>
+  </si>
+  <si>
+    <t>1 Pedro 1, 18-25</t>
+  </si>
+  <si>
+    <t>Mc 10, 45</t>
+  </si>
+  <si>
+    <t>Marcos 10, 32-45</t>
+  </si>
+  <si>
+    <t>1 Pedro 2, 2-5. 9-12</t>
+  </si>
+  <si>
+    <t>Salmo 99, 2. 3. 4. 5</t>
+  </si>
+  <si>
+    <t>Jn 8, 12</t>
+  </si>
+  <si>
+    <t>Marcos 10, 46-52</t>
+  </si>
+  <si>
+    <t>1 Pedro 4, 7-13</t>
+  </si>
+  <si>
+    <t>Salmo 95, 10. 11-12. 13</t>
+  </si>
+  <si>
+    <t>Jn 15, 16</t>
+  </si>
+  <si>
+    <t>Marcos 11, 11-26</t>
+  </si>
+  <si>
+    <t>Judas: 17. 20b-25</t>
+  </si>
+  <si>
+    <t>Salmo 62, 2. 3-4. 5-6</t>
+  </si>
+  <si>
+    <t>Col 3, 16. 17</t>
+  </si>
+  <si>
+    <t>Marcos 11, 27-33</t>
+  </si>
+  <si>
+    <t>2 Pedro 1, 1-7</t>
+  </si>
+  <si>
+    <t>Salmo 90, 1-2. 14-15ab. 15c-16</t>
+  </si>
+  <si>
+    <t>Ap 1, 5ab</t>
+  </si>
+  <si>
+    <t>Marcos 12, 1-12</t>
+  </si>
+  <si>
+    <t>2 Pedro 3 ,12-15a. 17-18</t>
+  </si>
+  <si>
+    <t>Salmo 89, 2. 3-4. 10. 14 y 16</t>
+  </si>
+  <si>
+    <t>Marcos 12, 13-17</t>
+  </si>
+  <si>
+    <t>2 Timoteo 1, 1-3. 6-12</t>
+  </si>
+  <si>
+    <t>Salmo 122, 1-2a. 2</t>
+  </si>
+  <si>
+    <t>Marcos 12, 18-27</t>
+  </si>
+  <si>
+    <t>2 Timoteo 2, 8-15</t>
+  </si>
+  <si>
+    <t>Salmo 24, 4bc-5ab. 8-9. 10 y 14</t>
+  </si>
+  <si>
+    <t>Marcos 12, 28b-34</t>
+  </si>
+  <si>
+    <t>2 Timoteo 3, 10-17</t>
+  </si>
+  <si>
+    <t>Salmo 118, 157. 160. 161. 165. 166. 168</t>
+  </si>
+  <si>
+    <t>Marcos 12, 35-37</t>
+  </si>
+  <si>
+    <t>2 Timoteo 4, 1-8</t>
+  </si>
+  <si>
+    <t>Salmo 70, 8-9. 14-15ab. 16-17. 22</t>
+  </si>
+  <si>
+    <t>Mt 5, 3</t>
+  </si>
+  <si>
+    <t>Marcos 12, 38-44</t>
+  </si>
+  <si>
+    <t>1 Reyes 17, 1-6</t>
+  </si>
+  <si>
+    <t>Salmo 120, 1-2. 3-4. 5-6. 7-8</t>
+  </si>
+  <si>
+    <t>Mt 5, 12</t>
+  </si>
+  <si>
+    <t>Mateo 5, 1-12</t>
+  </si>
+  <si>
+    <t>1 Reyes 17, 7-16</t>
+  </si>
+  <si>
+    <t>Salmo 4, 2-3. 4-5. 7-8</t>
+  </si>
+  <si>
+    <t>Mt 5, 16</t>
+  </si>
+  <si>
+    <t>1 Reyes 18, 20-39</t>
+  </si>
+  <si>
+    <t>Salmo 15, 1-2a. 4. 5 y 8. 11</t>
+  </si>
+  <si>
+    <t>Sal 24, 4b. 5a</t>
+  </si>
+  <si>
+    <t>Mateo 5, 17-19</t>
+  </si>
+  <si>
+    <t>1 Reyes 18, 41-46</t>
+  </si>
+  <si>
+    <t>Salmo 64, 10. 10-11. 12-13</t>
+  </si>
+  <si>
+    <t>Mateo 5, 20-26</t>
+  </si>
+  <si>
+    <t>1 Reyes 19, 9a. 11-16</t>
+  </si>
+  <si>
+    <t>Salmo 26, 7-8. 8-9. 13-14</t>
+  </si>
+  <si>
+    <t>Flp 2, 15. 16</t>
+  </si>
+  <si>
+    <t>Mateo 5, 27-32</t>
+  </si>
+  <si>
+    <t>1 Reyes 19, 19-21</t>
+  </si>
+  <si>
+    <t>Salmo 15, 1-2a y 5. 7-8. 9-10</t>
+  </si>
+  <si>
+    <t>Sal 118, 36. 29</t>
+  </si>
+  <si>
+    <t>Mateo 5, 33-37</t>
+  </si>
+  <si>
+    <t>1 Reyes 21, 1-16</t>
+  </si>
+  <si>
+    <t>Salmo 5, 2-3. 5-6. 7</t>
+  </si>
+  <si>
+    <t>Mateo 5, 38-42</t>
+  </si>
+  <si>
+    <t>1 Reyes 21, 17-29</t>
+  </si>
+  <si>
+    <t>Salmo 50, 3-4. 5-6a. 11 y 16</t>
+  </si>
+  <si>
+    <t>Mateo 5, 43-48</t>
+  </si>
+  <si>
+    <t>2 Reyes 2, 1. 6-14</t>
+  </si>
+  <si>
+    <t>Salmo 30, 20. 21. 24</t>
+  </si>
+  <si>
+    <t>Mateo 6, 1-6. 16-18</t>
+  </si>
+  <si>
+    <t>Sirácida 48, 1-15</t>
+  </si>
+  <si>
+    <t>Salmo 96, 1-2. 3-4. 5-6. 7</t>
+  </si>
+  <si>
+    <t>Rm 8, 15</t>
+  </si>
+  <si>
+    <t>Mateo 6, 7-15</t>
+  </si>
+  <si>
+    <t>2 Reyes 11, 1-4. 9-18. 20</t>
+  </si>
+  <si>
+    <t>Salmo 131, 11. 12. 13-14. 17-18</t>
+  </si>
+  <si>
+    <t>Mateo 6, 19-23</t>
+  </si>
+  <si>
+    <t>2 Crónicas 24, 17-25</t>
+  </si>
+  <si>
+    <t>Salmo 88, 4-5. 29-30. 31-32. 33-34</t>
+  </si>
+  <si>
+    <t>2 Reyes 17, 5-8. 13-15.18</t>
+  </si>
+  <si>
+    <t>Salmo 59, 3. 4-5. 12-13</t>
+  </si>
+  <si>
+    <t>Mateo 7, 1-5</t>
+  </si>
+  <si>
+    <t>2 Reyes 19, 9-11. 14-21. 31-35. 36</t>
+  </si>
+  <si>
+    <t>Salmo 47, 2-3a. 3b-4. 10-11</t>
+  </si>
+  <si>
+    <t>Mateo 7, 6. 12-14</t>
+  </si>
+  <si>
+    <t>2 Reyes 22, 13; 23, 1-3</t>
+  </si>
+  <si>
+    <t>Salmo 118, 33. 34. 35. 36. 37. 40</t>
+  </si>
+  <si>
+    <t>Jn 15, 4a. 5</t>
+  </si>
+  <si>
+    <t>Mateo 7, 15-20</t>
+  </si>
+  <si>
+    <t>2 Reyes 24, 8-17</t>
+  </si>
+  <si>
+    <t>Salmo 78, 1-2. 3-5. 8. 9</t>
+  </si>
+  <si>
+    <t>Mateo 7, 21-29</t>
+  </si>
+  <si>
+    <t>2 Reyes 25, 1-12</t>
+  </si>
+  <si>
+    <t>Salmo 136, 1-2. 3. 4-5. 6</t>
+  </si>
+  <si>
+    <t>Mateo 8, 1-4</t>
+  </si>
+  <si>
+    <t>Lamentaciones 2, 2. 10-14. 18-19</t>
+  </si>
+  <si>
+    <t>Salmo 73, 1-2. 3-5a. 5b-7. 20-21</t>
+  </si>
+  <si>
+    <t>Mateo 8, 5-17</t>
+  </si>
+  <si>
+    <t>Amós 2, 6-10. 13-16</t>
+  </si>
+  <si>
+    <t>Salmo 49, 16-17. 18-19. 20-21. 22-23</t>
+  </si>
+  <si>
+    <t>Sal 94, 8</t>
+  </si>
+  <si>
+    <t>Mateo 8, 18-22</t>
+  </si>
+  <si>
+    <t>Amós 3, 1-8; 4, 11-12</t>
+  </si>
+  <si>
+    <t>Salmo 5, 5-6. 7. 8</t>
+  </si>
+  <si>
+    <t>Sal 129, 5</t>
+  </si>
+  <si>
+    <t>Mateo 8, 23-27</t>
+  </si>
+  <si>
+    <t>Amós 5, 14-15. 21-24</t>
+  </si>
+  <si>
+    <t>Salmo 49, 7. 8-9. 10-11. 12-13. 16-17</t>
+  </si>
+  <si>
+    <t>St 1, 18</t>
+  </si>
+  <si>
+    <t>Mateo 8, 28-34</t>
+  </si>
+  <si>
+    <t>Amós 7, 10-17</t>
+  </si>
+  <si>
+    <t>Salmo 18, 8. 9. 10. 11</t>
+  </si>
+  <si>
+    <t>Mateo 9, 1-8</t>
+  </si>
+  <si>
+    <t>Amós 8, 4-6. 9-12</t>
+  </si>
+  <si>
+    <t>Salmo 118, 2. 10. 20. 30. 40. 131</t>
+  </si>
+  <si>
+    <t>Mt 11, 28</t>
+  </si>
+  <si>
+    <t>Amós 9, 11-15</t>
+  </si>
+  <si>
+    <t>Salmo 84, 9. 11-12. 13-14</t>
+  </si>
+  <si>
+    <t>Mateo 9, 14-17</t>
+  </si>
+  <si>
+    <t>Oseas 2, 16. 17b-18. 21-22</t>
+  </si>
+  <si>
+    <t>Salmo 144, 2-3. 4-5. 6-7. 8-9</t>
+  </si>
+  <si>
+    <t>Mateo 9, 18-26</t>
+  </si>
+  <si>
+    <t>Oseas 8, 4-7. 11. 13</t>
+  </si>
+  <si>
+    <t>Salmo 113B, 3-4. 5-6. 7-8. 9-10</t>
+  </si>
+  <si>
+    <t>Mateo 9, 32-38</t>
+  </si>
+  <si>
+    <t>Oseas 10, 1-3. 7-8. 12</t>
+  </si>
+  <si>
+    <t>Salmo 104, 2-3. 4-5. 6-7</t>
+  </si>
+  <si>
+    <t>Mateo 10, 1-7</t>
+  </si>
+  <si>
+    <t>Oseas 11, 1-4. 8-9</t>
+  </si>
+  <si>
+    <t>Salmo 79, 2ac y 3b. 15-16</t>
+  </si>
+  <si>
+    <t>Mateo 10, 7-15</t>
+  </si>
+  <si>
+    <t>Oseas 14, 2-10</t>
+  </si>
+  <si>
+    <t>Salmo 50, 3-4. 8-9. 12-13. 14 y 17</t>
+  </si>
+  <si>
+    <t>Jn 16, 13; 14, 26</t>
+  </si>
+  <si>
+    <t>Mateo 10, 16-23</t>
+  </si>
+  <si>
+    <t>Isaías 6, 1-8</t>
+  </si>
+  <si>
+    <t>Salmo 92, 1. 1-2. 5</t>
+  </si>
+  <si>
+    <t>1P 4, 14</t>
+  </si>
+  <si>
+    <t>Mateo 10, 24-33</t>
+  </si>
+  <si>
+    <t>Isaías 1, 10-17</t>
+  </si>
+  <si>
+    <t>Mt, 5, 10</t>
+  </si>
+  <si>
+    <t>Mateo 10, 34—11, 1</t>
+  </si>
+  <si>
+    <t>Isaías 7, 1-9</t>
+  </si>
+  <si>
+    <t>Salmo 47, 2-3a. 3b-4. 5-6. 7-8</t>
+  </si>
+  <si>
+    <t>Mateo 11, 20-24</t>
+  </si>
+  <si>
+    <t>Isaías 10, 5-7. 13-16</t>
+  </si>
+  <si>
+    <t>Salmo 93, 5-6. 7-8. 9-10. 14-15</t>
+  </si>
+  <si>
+    <t>Mateo 11, 25-27</t>
+  </si>
+  <si>
+    <t>Isaías 26, 7-9. 12. 16-19</t>
+  </si>
+  <si>
+    <t>Salmo 101, 13-14ab y 15. 16-18. 19-21</t>
+  </si>
+  <si>
+    <t>Mateo 11, 28-30</t>
+  </si>
+  <si>
+    <t>Isaías 38, 1-6. 21-22. 7-8</t>
+  </si>
+  <si>
+    <t>Isaías 38, 10. 11. 12. 16</t>
+  </si>
+  <si>
+    <t>Mateo 12, 1-8</t>
+  </si>
+  <si>
+    <t>Miqueas 2, 1-5</t>
+  </si>
+  <si>
+    <t>Salmo 9, 22-23. 24-25. 28-29. 35</t>
+  </si>
+  <si>
+    <t>Mateo 12, 14-21</t>
+  </si>
+  <si>
+    <t>Miqueas 6, 1-4. 6-8</t>
+  </si>
+  <si>
+    <t>Salmo 49, 5-6. 8-9. 16bc-17. 21 y 23</t>
+  </si>
+  <si>
+    <t>Mateo 12, 38-42</t>
+  </si>
+  <si>
+    <t>Miqueas 7, 14-15. 18-20</t>
+  </si>
+  <si>
+    <t>Salmo 84, 2-4. 5-6. 7-8</t>
+  </si>
+  <si>
+    <t>Mateo 12, 46-50</t>
+  </si>
+  <si>
+    <t>Jeremías 1, 1. 4-10</t>
+  </si>
+  <si>
+    <t>Salmo 70, 1-2. 3-4a. 5-6ab. 15ab y 17</t>
+  </si>
+  <si>
+    <t>Jeremías 2, 1-3. 7-8. 12-13</t>
+  </si>
+  <si>
+    <t>Salmo 35, 6-7ab. 8-9. 10-11</t>
+  </si>
+  <si>
+    <t>Mateo 13, 10-17</t>
+  </si>
+  <si>
+    <t>Jeremías 3, 14-17</t>
+  </si>
+  <si>
+    <t>Jeremías 31, 10. 11 -12. 13</t>
+  </si>
+  <si>
+    <t>Mateo 13, 18-23</t>
+  </si>
+  <si>
+    <t>Jeremías 7, 1-11</t>
+  </si>
+  <si>
+    <t>Salmo 83, 3. 4. 5-6 y 8. 11</t>
+  </si>
+  <si>
+    <t>Jeremías 13, 1-11</t>
+  </si>
+  <si>
+    <t>Deuteronomio 32, 18-19. 20. 21</t>
+  </si>
+  <si>
+    <t>Mateo 13, 31-35</t>
+  </si>
+  <si>
+    <t>Jeremías 14, 17-22</t>
+  </si>
+  <si>
+    <t>Salmo 78, 8. 9. 11 y 13</t>
+  </si>
+  <si>
+    <t>Mateo 13, 36-43</t>
+  </si>
+  <si>
+    <t>Jeremías 15, 10. 16-21</t>
+  </si>
+  <si>
+    <t>Salmo 58, 23. 4-5a. 10-11. 17. 18</t>
+  </si>
+  <si>
+    <t>Jn 15, 15</t>
+  </si>
+  <si>
+    <t>Jeremías 18, 1-6</t>
+  </si>
+  <si>
+    <t>Salmo 145, 1-2. 3-4. 5-6</t>
+  </si>
+  <si>
+    <t>Mateo 13, 47-53</t>
+  </si>
+  <si>
+    <t>Jeremías 26, 1-9</t>
+  </si>
+  <si>
+    <t>Salmo 68, 5. 8-10. 14</t>
+  </si>
+  <si>
+    <t>1P 1, 25</t>
+  </si>
+  <si>
+    <t>Mateo 13, 54-58</t>
+  </si>
+  <si>
+    <t>Jeremías 26, 11-16. 24</t>
+  </si>
+  <si>
+    <t>Salmo 68, 15-16. 30-31. 33-34</t>
+  </si>
+  <si>
+    <t>Mt 5, 10</t>
+  </si>
+  <si>
+    <t>Mateo 14, 1-12</t>
+  </si>
+  <si>
+    <t>Jeremías 28, 1-17</t>
+  </si>
+  <si>
+    <t>Salmo 118, 29. 43. 79. 80. 95. 102</t>
+  </si>
+  <si>
+    <t>Jeremías 30, 1-2. 12-15. 18-22</t>
+  </si>
+  <si>
+    <t>Salmo 101, 16-18. 19-21. 29 y 22-23</t>
+  </si>
+  <si>
+    <t>Jn 1, 49b</t>
+  </si>
+  <si>
+    <t>Mateo 14, 22-36 / Mateo 15, 1-2. 10-14</t>
+  </si>
+  <si>
+    <t>Jeremías 31, 1-7</t>
+  </si>
+  <si>
+    <t>Jeremías 31. 10. 11-12ab. 13</t>
+  </si>
+  <si>
+    <t>Jeremías 31, 31-34</t>
+  </si>
+  <si>
+    <t>Salmo 50, 12-13. 14-15. 18-19</t>
+  </si>
+  <si>
+    <t>Mt 16, 18</t>
+  </si>
+  <si>
+    <t>Mateo 16, 13-23</t>
+  </si>
+  <si>
+    <t>Nahum 2, 1. 3; 3, 1-3. 6-7</t>
+  </si>
+  <si>
+    <t>Deuteronomio 32, 35-36. 39. 41 </t>
+  </si>
+  <si>
+    <t>Mateo 16, 24-28</t>
+  </si>
+  <si>
+    <t>Habacuc 1, 12—2, 4</t>
+  </si>
+  <si>
+    <t>Salmo 9, 8-9. 10-11. 12-13</t>
+  </si>
+  <si>
+    <t>Mateo 17, 14-20</t>
+  </si>
+  <si>
+    <t>Ezequiel 1, 2-5. 24-28</t>
+  </si>
+  <si>
+    <t>Salmo 148, 1-2. 11-12. 12-14</t>
+  </si>
+  <si>
+    <t>2Ts 2, 14</t>
+  </si>
+  <si>
+    <t>Mateo 17, 22-27</t>
+  </si>
+  <si>
+    <t>Ezequiel 2, 8—3, 4</t>
+  </si>
+  <si>
+    <t>Salmo 118, 14. 24. 72. 103. 111. 131</t>
+  </si>
+  <si>
+    <t>Mt 11, 29</t>
+  </si>
+  <si>
+    <t>Mateo 18, 1-5. 10. 12-14</t>
+  </si>
+  <si>
+    <t>Ezequiel 9, 1-7; 10, 18-22</t>
+  </si>
+  <si>
+    <t>Salmo 112, 1-2. 3-4. 5-6</t>
+  </si>
+  <si>
+    <t>Ezequiel 12, 1-12</t>
+  </si>
+  <si>
+    <t>Salmo 77, 56-57. 58-59. 61-62</t>
+  </si>
+  <si>
+    <t>Sal 118, 135</t>
+  </si>
+  <si>
+    <t>Mateo 18, 21 - 19, 1</t>
+  </si>
+  <si>
+    <t>Ezequiel 16, 1-15. 60. 63  / Ezequiel Ez 16, 59-63</t>
+  </si>
+  <si>
+    <t>Isaías 12, 2-3. 4bcd. 5-6 </t>
+  </si>
+  <si>
+    <t>Mateo 19, 3-12</t>
+  </si>
+  <si>
+    <t>Ezequiel 18, 1-10. 13b. 30-32</t>
+  </si>
+  <si>
+    <t>Mateo 19, 13-15</t>
+  </si>
+  <si>
+    <t>Ezequiel 24, 15-24</t>
+  </si>
+  <si>
+    <t>Mateo 19, 16-22</t>
+  </si>
+  <si>
+    <t>Ezequiel 28, 1-10</t>
+  </si>
+  <si>
+    <t>Deuteronomio 32, 26-27. 27-28. 30. 35-36</t>
+  </si>
+  <si>
+    <t>Mateo 19, 23-30</t>
+  </si>
+  <si>
+    <t>Ezequiel 34, 1-11</t>
+  </si>
+  <si>
+    <t>Ezequiel 36, 23-28</t>
+  </si>
+  <si>
+    <t>Ezequiel 37, 1-14</t>
+  </si>
+  <si>
+    <t>Salmo 106, 2-3. 4-5. 6-7. 8-9</t>
+  </si>
+  <si>
+    <t>Ezequiel 43, 1-7a</t>
+  </si>
+  <si>
+    <t>Salmo 84, 9ab-10. 11-12. 13-14</t>
+  </si>
+  <si>
+    <t>Mt 23, 9. 10</t>
+  </si>
+  <si>
+    <t>Sal 24, 4. 5</t>
+  </si>
+  <si>
+    <t>https://servicioskoinonia.org/leccionario/Libro_04.html</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1461,6 +2577,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1479,18 +2603,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4126,210 +5256,3938 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AFBACE-E0D0-47E0-A7DB-4F0CC57B5A5B}">
-  <dimension ref="A2:G13"/>
+  <dimension ref="A2:H205"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <f t="shared" ref="B2:B56" si="0">_xlfn.CONCAT("TO-s",A2,"-PAR")</f>
+        <v>TO-s1-PAR</v>
+      </c>
+      <c r="C2" t="s">
         <v>430</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>451</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>421</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>422</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>429</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s1-PAR</v>
+      </c>
+      <c r="C3" t="s">
         <v>424</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>452</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>426</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>427</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>429</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s1-PAR</v>
+      </c>
+      <c r="C4" t="s">
         <v>431</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>436</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>437</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>438</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>429</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s1-PAR</v>
+      </c>
+      <c r="C5" t="s">
         <v>432</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>440</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>441</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>442</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>429</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s1-PAR</v>
+      </c>
+      <c r="C6" t="s">
         <v>433</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>444</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>445</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>446</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>429</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s1-PAR</v>
+      </c>
+      <c r="C7" t="s">
         <v>434</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>448</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>449</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>435</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s2-PAR</v>
+      </c>
+      <c r="C8" t="s">
         <v>430</v>
       </c>
-      <c r="G8">
-        <f t="shared" ref="G8:G13" si="0">IF(J8="",I8,_xlfn.CONCAT(I8," / ",J8))</f>
+      <c r="D8" t="s">
+        <v>453</v>
+      </c>
+      <c r="E8" t="s">
+        <v>454</v>
+      </c>
+      <c r="F8" t="s">
+        <v>455</v>
+      </c>
+      <c r="G8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:H13" si="1">IF(K8="",J8,_xlfn.CONCAT(J8," / ",K8))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>435</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s2-PAR</v>
+      </c>
+      <c r="C9" t="s">
         <v>424</v>
       </c>
-      <c r="G9">
+      <c r="D9" t="s">
+        <v>457</v>
+      </c>
+      <c r="E9" t="s">
+        <v>458</v>
+      </c>
+      <c r="F9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G9" t="s">
+        <v>460</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="str">
         <f t="shared" si="0"/>
+        <v>TO-s2-PAR</v>
+      </c>
+      <c r="C10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D10" t="s">
+        <v>461</v>
+      </c>
+      <c r="E10" t="s">
+        <v>462</v>
+      </c>
+      <c r="F10" t="s">
+        <v>442</v>
+      </c>
+      <c r="G10" t="s">
+        <v>463</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>435</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s2-PAR</v>
+      </c>
+      <c r="C11" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" t="s">
+        <v>464</v>
+      </c>
+      <c r="E11" t="s">
+        <v>465</v>
+      </c>
+      <c r="F11" t="s">
+        <v>466</v>
+      </c>
+      <c r="G11" t="s">
+        <v>467</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s2-PAR</v>
+      </c>
+      <c r="C12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D12" t="s">
+        <v>468</v>
+      </c>
+      <c r="E12" t="s">
+        <v>469</v>
+      </c>
+      <c r="F12" t="s">
+        <v>470</v>
+      </c>
+      <c r="G12" t="s">
+        <v>471</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s2-PAR</v>
+      </c>
+      <c r="C13" t="s">
+        <v>434</v>
+      </c>
+      <c r="D13" t="s">
+        <v>472</v>
+      </c>
+      <c r="E13" t="s">
+        <v>473</v>
+      </c>
+      <c r="F13" t="s">
+        <v>474</v>
+      </c>
+      <c r="G13" t="s">
+        <v>475</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s3-PAR</v>
+      </c>
+      <c r="C14" t="s">
+        <v>430</v>
+      </c>
+      <c r="D14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E14" t="s">
+        <v>477</v>
+      </c>
+      <c r="F14" t="s">
+        <v>466</v>
+      </c>
+      <c r="G14" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s3-PAR</v>
+      </c>
+      <c r="C15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D15" t="s">
+        <v>480</v>
+      </c>
+      <c r="E15" t="s">
+        <v>479</v>
+      </c>
+      <c r="F15" t="s">
+        <v>481</v>
+      </c>
+      <c r="G15" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s3-PAR</v>
+      </c>
+      <c r="C16" t="s">
         <v>431</v>
       </c>
-      <c r="G10">
+      <c r="D16" t="s">
+        <v>483</v>
+      </c>
+      <c r="E16" t="s">
+        <v>484</v>
+      </c>
+      <c r="F16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G16" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>435</v>
-      </c>
-      <c r="B11" t="s">
+        <v>TO-s3-PAR</v>
+      </c>
+      <c r="C17" t="s">
         <v>432</v>
       </c>
-      <c r="G11">
+      <c r="D17" t="s">
+        <v>486</v>
+      </c>
+      <c r="E17" t="s">
+        <v>487</v>
+      </c>
+      <c r="F17" t="s">
+        <v>488</v>
+      </c>
+      <c r="G17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>435</v>
-      </c>
-      <c r="B12" t="s">
+        <v>TO-s3-PAR</v>
+      </c>
+      <c r="C18" t="s">
         <v>433</v>
       </c>
-      <c r="G12">
+      <c r="D18" t="s">
+        <v>490</v>
+      </c>
+      <c r="E18" t="s">
+        <v>491</v>
+      </c>
+      <c r="F18" t="s">
+        <v>481</v>
+      </c>
+      <c r="G18" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>435</v>
-      </c>
-      <c r="B13" t="s">
+        <v>TO-s3-PAR</v>
+      </c>
+      <c r="C19" t="s">
         <v>434</v>
       </c>
-      <c r="G13">
+      <c r="D19" t="s">
+        <v>493</v>
+      </c>
+      <c r="E19" t="s">
+        <v>494</v>
+      </c>
+      <c r="F19" t="s">
+        <v>495</v>
+      </c>
+      <c r="G19" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>TO-s4-PAR</v>
+      </c>
+      <c r="C20" t="s">
+        <v>430</v>
+      </c>
+      <c r="D20" t="s">
+        <v>497</v>
+      </c>
+      <c r="E20" t="s">
+        <v>498</v>
+      </c>
+      <c r="F20" t="s">
+        <v>446</v>
+      </c>
+      <c r="G20" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s4-PAR</v>
+      </c>
+      <c r="C21" t="s">
+        <v>424</v>
+      </c>
+      <c r="D21" t="s">
+        <v>500</v>
+      </c>
+      <c r="E21" t="s">
+        <v>501</v>
+      </c>
+      <c r="F21" t="s">
+        <v>502</v>
+      </c>
+      <c r="G21" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s4-PAR</v>
+      </c>
+      <c r="C22" t="s">
+        <v>431</v>
+      </c>
+      <c r="D22" t="s">
+        <v>504</v>
+      </c>
+      <c r="E22" t="s">
+        <v>505</v>
+      </c>
+      <c r="F22" t="s">
+        <v>438</v>
+      </c>
+      <c r="G22" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s4-PAR</v>
+      </c>
+      <c r="C23" t="s">
+        <v>432</v>
+      </c>
+      <c r="D23" t="s">
+        <v>507</v>
+      </c>
+      <c r="E23" t="s">
+        <v>508</v>
+      </c>
+      <c r="F23" t="s">
+        <v>422</v>
+      </c>
+      <c r="G23" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>4</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s4-PAR</v>
+      </c>
+      <c r="C24" t="s">
+        <v>433</v>
+      </c>
+      <c r="D24" t="s">
+        <v>510</v>
+      </c>
+      <c r="E24" t="s">
+        <v>511</v>
+      </c>
+      <c r="F24" t="s">
+        <v>512</v>
+      </c>
+      <c r="G24" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s4-PAR</v>
+      </c>
+      <c r="C25" t="s">
+        <v>434</v>
+      </c>
+      <c r="D25" t="s">
+        <v>515</v>
+      </c>
+      <c r="E25" t="s">
+        <v>514</v>
+      </c>
+      <c r="F25" t="s">
+        <v>438</v>
+      </c>
+      <c r="G25" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s5-PAR</v>
+      </c>
+      <c r="C26" t="s">
+        <v>430</v>
+      </c>
+      <c r="D26" t="s">
+        <v>517</v>
+      </c>
+      <c r="E26" t="s">
+        <v>518</v>
+      </c>
+      <c r="F26" t="s">
+        <v>442</v>
+      </c>
+      <c r="G26" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s5-PAR</v>
+      </c>
+      <c r="C27" t="s">
+        <v>424</v>
+      </c>
+      <c r="D27" t="s">
+        <v>520</v>
+      </c>
+      <c r="E27" t="s">
+        <v>521</v>
+      </c>
+      <c r="F27" t="s">
+        <v>522</v>
+      </c>
+      <c r="G27" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>5</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s5-PAR</v>
+      </c>
+      <c r="C28" t="s">
+        <v>431</v>
+      </c>
+      <c r="D28" t="s">
+        <v>524</v>
+      </c>
+      <c r="E28" t="s">
+        <v>525</v>
+      </c>
+      <c r="F28" t="s">
+        <v>526</v>
+      </c>
+      <c r="G28" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s5-PAR</v>
+      </c>
+      <c r="C29" t="s">
+        <v>432</v>
+      </c>
+      <c r="D29" t="s">
+        <v>528</v>
+      </c>
+      <c r="E29" t="s">
+        <v>529</v>
+      </c>
+      <c r="F29" t="s">
+        <v>530</v>
+      </c>
+      <c r="G29" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s5-PAR</v>
+      </c>
+      <c r="C30" t="s">
+        <v>433</v>
+      </c>
+      <c r="D30" t="s">
+        <v>532</v>
+      </c>
+      <c r="E30" t="s">
+        <v>533</v>
+      </c>
+      <c r="F30" t="s">
+        <v>474</v>
+      </c>
+      <c r="G30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s5-PAR</v>
+      </c>
+      <c r="C31" t="s">
+        <v>434</v>
+      </c>
+      <c r="D31" t="s">
+        <v>535</v>
+      </c>
+      <c r="E31" t="s">
+        <v>536</v>
+      </c>
+      <c r="F31" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>6</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s6-PAR</v>
+      </c>
+      <c r="C32" t="s">
+        <v>430</v>
+      </c>
+      <c r="D32" t="s">
+        <v>539</v>
+      </c>
+      <c r="E32" t="s">
+        <v>540</v>
+      </c>
+      <c r="F32" t="s">
+        <v>169</v>
+      </c>
+      <c r="G32" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>6</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s6-PAR</v>
+      </c>
+      <c r="C33" t="s">
+        <v>424</v>
+      </c>
+      <c r="D33" t="s">
+        <v>542</v>
+      </c>
+      <c r="E33" t="s">
+        <v>543</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>6</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s6-PAR</v>
+      </c>
+      <c r="C34" t="s">
+        <v>431</v>
+      </c>
+      <c r="D34" t="s">
+        <v>545</v>
+      </c>
+      <c r="E34" t="s">
+        <v>546</v>
+      </c>
+      <c r="F34" t="s">
+        <v>459</v>
+      </c>
+      <c r="G34" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>6</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s6-PAR</v>
+      </c>
+      <c r="C35" t="s">
+        <v>432</v>
+      </c>
+      <c r="D35" t="s">
+        <v>548</v>
+      </c>
+      <c r="E35" t="s">
+        <v>549</v>
+      </c>
+      <c r="F35" t="s">
+        <v>550</v>
+      </c>
+      <c r="G35" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>6</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s6-PAR</v>
+      </c>
+      <c r="C36" t="s">
+        <v>433</v>
+      </c>
+      <c r="D36" t="s">
+        <v>552</v>
+      </c>
+      <c r="E36" t="s">
+        <v>553</v>
+      </c>
+      <c r="F36" t="s">
+        <v>554</v>
+      </c>
+      <c r="G36" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>6</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s6-PAR</v>
+      </c>
+      <c r="C37" t="s">
+        <v>434</v>
+      </c>
+      <c r="D37" t="s">
+        <v>556</v>
+      </c>
+      <c r="E37" t="s">
+        <v>557</v>
+      </c>
+      <c r="F37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>7</v>
+      </c>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s7-PAR</v>
+      </c>
+      <c r="C38" t="s">
+        <v>430</v>
+      </c>
+      <c r="D38" t="s">
+        <v>559</v>
+      </c>
+      <c r="E38" t="s">
+        <v>560</v>
+      </c>
+      <c r="F38" t="s">
+        <v>466</v>
+      </c>
+      <c r="G38" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s7-PAR</v>
+      </c>
+      <c r="C39" t="s">
+        <v>424</v>
+      </c>
+      <c r="D39" t="s">
+        <v>562</v>
+      </c>
+      <c r="E39" t="s">
+        <v>563</v>
+      </c>
+      <c r="F39" t="s">
+        <v>564</v>
+      </c>
+      <c r="G39" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>7</v>
+      </c>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s7-PAR</v>
+      </c>
+      <c r="C40" t="s">
+        <v>431</v>
+      </c>
+      <c r="D40" t="s">
+        <v>566</v>
+      </c>
+      <c r="E40" t="s">
+        <v>567</v>
+      </c>
+      <c r="F40" t="s">
+        <v>169</v>
+      </c>
+      <c r="G40" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s7-PAR</v>
+      </c>
+      <c r="C41" t="s">
+        <v>432</v>
+      </c>
+      <c r="D41" t="s">
+        <v>569</v>
+      </c>
+      <c r="E41" t="s">
+        <v>570</v>
+      </c>
+      <c r="F41" t="s">
+        <v>427</v>
+      </c>
+      <c r="G41" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s7-PAR</v>
+      </c>
+      <c r="C42" t="s">
+        <v>433</v>
+      </c>
+      <c r="D42" t="s">
+        <v>572</v>
+      </c>
+      <c r="E42" t="s">
+        <v>573</v>
+      </c>
+      <c r="F42" t="s">
+        <v>526</v>
+      </c>
+      <c r="G42" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s7-PAR</v>
+      </c>
+      <c r="C43" t="s">
+        <v>434</v>
+      </c>
+      <c r="D43" t="s">
+        <v>575</v>
+      </c>
+      <c r="E43" t="s">
+        <v>576</v>
+      </c>
+      <c r="F43" t="s">
+        <v>481</v>
+      </c>
+      <c r="G43" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>8</v>
+      </c>
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s8-PAR</v>
+      </c>
+      <c r="C44" t="s">
+        <v>430</v>
+      </c>
+      <c r="D44" t="s">
+        <v>578</v>
+      </c>
+      <c r="E44" t="s">
+        <v>579</v>
+      </c>
+      <c r="F44" t="s">
+        <v>580</v>
+      </c>
+      <c r="G44" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>8</v>
+      </c>
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s8-PAR</v>
+      </c>
+      <c r="C45" t="s">
+        <v>424</v>
+      </c>
+      <c r="D45" t="s">
+        <v>582</v>
+      </c>
+      <c r="E45" t="s">
+        <v>583</v>
+      </c>
+      <c r="F45" t="s">
+        <v>481</v>
+      </c>
+      <c r="G45" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>8</v>
+      </c>
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s8-PAR</v>
+      </c>
+      <c r="C46" t="s">
+        <v>431</v>
+      </c>
+      <c r="D46" t="s">
+        <v>585</v>
+      </c>
+      <c r="E46" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" t="s">
+        <v>586</v>
+      </c>
+      <c r="G46" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>8</v>
+      </c>
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s8-PAR</v>
+      </c>
+      <c r="C47" t="s">
+        <v>432</v>
+      </c>
+      <c r="D47" t="s">
+        <v>588</v>
+      </c>
+      <c r="E47" t="s">
+        <v>589</v>
+      </c>
+      <c r="F47" t="s">
+        <v>590</v>
+      </c>
+      <c r="G47" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>8</v>
+      </c>
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s8-PAR</v>
+      </c>
+      <c r="C48" t="s">
+        <v>433</v>
+      </c>
+      <c r="D48" t="s">
+        <v>592</v>
+      </c>
+      <c r="E48" t="s">
+        <v>593</v>
+      </c>
+      <c r="F48" t="s">
+        <v>594</v>
+      </c>
+      <c r="G48" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>8</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s8-PAR</v>
+      </c>
+      <c r="C49" t="s">
+        <v>434</v>
+      </c>
+      <c r="D49" t="s">
+        <v>596</v>
+      </c>
+      <c r="E49" t="s">
+        <v>597</v>
+      </c>
+      <c r="F49" t="s">
+        <v>598</v>
+      </c>
+      <c r="G49" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s9-PAR</v>
+      </c>
+      <c r="C50" t="s">
+        <v>430</v>
+      </c>
+      <c r="D50" t="s">
+        <v>600</v>
+      </c>
+      <c r="E50" t="s">
+        <v>601</v>
+      </c>
+      <c r="F50" t="s">
+        <v>602</v>
+      </c>
+      <c r="G50" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>9</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s9-PAR</v>
+      </c>
+      <c r="C51" t="s">
+        <v>424</v>
+      </c>
+      <c r="D51" t="s">
+        <v>604</v>
+      </c>
+      <c r="E51" t="s">
+        <v>605</v>
+      </c>
+      <c r="F51" t="s">
+        <v>459</v>
+      </c>
+      <c r="G51" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>9</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s9-PAR</v>
+      </c>
+      <c r="C52" t="s">
+        <v>431</v>
+      </c>
+      <c r="D52" t="s">
+        <v>607</v>
+      </c>
+      <c r="E52" t="s">
+        <v>608</v>
+      </c>
+      <c r="F52" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>9</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s9-PAR</v>
+      </c>
+      <c r="C53" t="s">
+        <v>432</v>
+      </c>
+      <c r="D53" t="s">
+        <v>610</v>
+      </c>
+      <c r="E53" t="s">
+        <v>611</v>
+      </c>
+      <c r="F53" t="s">
+        <v>466</v>
+      </c>
+      <c r="G53" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>9</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s9-PAR</v>
+      </c>
+      <c r="C54" t="s">
+        <v>433</v>
+      </c>
+      <c r="D54" t="s">
+        <v>613</v>
+      </c>
+      <c r="E54" t="s">
+        <v>614</v>
+      </c>
+      <c r="F54" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>9</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s9-PAR</v>
+      </c>
+      <c r="C55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D55" t="s">
+        <v>616</v>
+      </c>
+      <c r="E55" t="s">
+        <v>617</v>
+      </c>
+      <c r="F55" t="s">
+        <v>618</v>
+      </c>
+      <c r="G55" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>10</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>TO-s10-PAR</v>
+      </c>
+      <c r="C56" t="s">
+        <v>430</v>
+      </c>
+      <c r="D56" t="s">
+        <v>620</v>
+      </c>
+      <c r="E56" t="s">
+        <v>621</v>
+      </c>
+      <c r="F56" t="s">
+        <v>622</v>
+      </c>
+      <c r="G56" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>10</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" ref="B51:B114" si="2">_xlfn.CONCAT("TO-s",A57,"-PAR")</f>
+        <v>TO-s10-PAR</v>
+      </c>
+      <c r="C57" t="s">
+        <v>424</v>
+      </c>
+      <c r="D57" t="s">
+        <v>624</v>
+      </c>
+      <c r="E57" t="s">
+        <v>625</v>
+      </c>
+      <c r="F57" t="s">
+        <v>626</v>
+      </c>
+      <c r="G57" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>10</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s10-PAR</v>
+      </c>
+      <c r="C58" t="s">
+        <v>431</v>
+      </c>
+      <c r="D58" t="s">
+        <v>627</v>
+      </c>
+      <c r="E58" t="s">
+        <v>628</v>
+      </c>
+      <c r="F58" t="s">
+        <v>629</v>
+      </c>
+      <c r="G58" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>10</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s10-PAR</v>
+      </c>
+      <c r="C59" t="s">
+        <v>432</v>
+      </c>
+      <c r="D59" t="s">
+        <v>631</v>
+      </c>
+      <c r="E59" t="s">
+        <v>632</v>
+      </c>
+      <c r="F59" t="s">
+        <v>133</v>
+      </c>
+      <c r="G59" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>10</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s10-PAR</v>
+      </c>
+      <c r="C60" t="s">
+        <v>433</v>
+      </c>
+      <c r="D60" t="s">
+        <v>634</v>
+      </c>
+      <c r="E60" t="s">
+        <v>635</v>
+      </c>
+      <c r="F60" t="s">
+        <v>636</v>
+      </c>
+      <c r="G60" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>10</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s10-PAR</v>
+      </c>
+      <c r="C61" t="s">
+        <v>434</v>
+      </c>
+      <c r="D61" t="s">
+        <v>638</v>
+      </c>
+      <c r="E61" t="s">
+        <v>639</v>
+      </c>
+      <c r="F61" t="s">
+        <v>640</v>
+      </c>
+      <c r="G61" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>11</v>
+      </c>
+      <c r="B62" t="str">
+        <f>_xlfn.CONCAT("TO-s",A62,"-PAR")</f>
+        <v>TO-s11-PAR</v>
+      </c>
+      <c r="C62" t="s">
+        <v>430</v>
+      </c>
+      <c r="D62" t="s">
+        <v>642</v>
+      </c>
+      <c r="E62" t="s">
+        <v>643</v>
+      </c>
+      <c r="F62" t="s">
+        <v>488</v>
+      </c>
+      <c r="G62" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>11</v>
+      </c>
+      <c r="B63" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s11-PAR</v>
+      </c>
+      <c r="C63" t="s">
+        <v>424</v>
+      </c>
+      <c r="D63" t="s">
+        <v>645</v>
+      </c>
+      <c r="E63" t="s">
+        <v>646</v>
+      </c>
+      <c r="F63" t="s">
+        <v>133</v>
+      </c>
+      <c r="G63" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>11</v>
+      </c>
+      <c r="B64" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s11-PAR</v>
+      </c>
+      <c r="C64" t="s">
+        <v>431</v>
+      </c>
+      <c r="D64" t="s">
+        <v>648</v>
+      </c>
+      <c r="E64" t="s">
+        <v>649</v>
+      </c>
+      <c r="F64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>11</v>
+      </c>
+      <c r="B65" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s11-PAR</v>
+      </c>
+      <c r="C65" t="s">
+        <v>432</v>
+      </c>
+      <c r="D65" t="s">
+        <v>651</v>
+      </c>
+      <c r="E65" t="s">
+        <v>652</v>
+      </c>
+      <c r="F65" t="s">
+        <v>653</v>
+      </c>
+      <c r="G65" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>11</v>
+      </c>
+      <c r="B66" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s11-PAR</v>
+      </c>
+      <c r="C66" t="s">
+        <v>433</v>
+      </c>
+      <c r="D66" t="s">
+        <v>655</v>
+      </c>
+      <c r="E66" t="s">
+        <v>656</v>
+      </c>
+      <c r="F66" t="s">
+        <v>618</v>
+      </c>
+      <c r="G66" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>11</v>
+      </c>
+      <c r="B67" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s11-PAR</v>
+      </c>
+      <c r="C67" t="s">
+        <v>434</v>
+      </c>
+      <c r="D67" t="s">
+        <v>658</v>
+      </c>
+      <c r="E67" t="s">
+        <v>659</v>
+      </c>
+      <c r="F67" t="s">
+        <v>580</v>
+      </c>
+      <c r="G67" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>12</v>
+      </c>
+      <c r="B68" t="str">
+        <f>_xlfn.CONCAT("TO-s",A68,"-PAR")</f>
+        <v>TO-s12-PAR</v>
+      </c>
+      <c r="C68" t="s">
+        <v>430</v>
+      </c>
+      <c r="D68" t="s">
+        <v>660</v>
+      </c>
+      <c r="E68" t="s">
+        <v>661</v>
+      </c>
+      <c r="F68" t="s">
+        <v>455</v>
+      </c>
+      <c r="G68" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>12</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s12-PAR</v>
+      </c>
+      <c r="C69" t="s">
+        <v>424</v>
+      </c>
+      <c r="D69" t="s">
+        <v>663</v>
+      </c>
+      <c r="E69" t="s">
+        <v>664</v>
+      </c>
+      <c r="F69" t="s">
+        <v>590</v>
+      </c>
+      <c r="G69" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>12</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s12-PAR</v>
+      </c>
+      <c r="C70" t="s">
+        <v>431</v>
+      </c>
+      <c r="D70" t="s">
+        <v>666</v>
+      </c>
+      <c r="E70" t="s">
+        <v>667</v>
+      </c>
+      <c r="F70" t="s">
+        <v>668</v>
+      </c>
+      <c r="G70" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>12</v>
+      </c>
+      <c r="B71" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s12-PAR</v>
+      </c>
+      <c r="C71" t="s">
+        <v>432</v>
+      </c>
+      <c r="D71" t="s">
+        <v>670</v>
+      </c>
+      <c r="E71" t="s">
+        <v>671</v>
+      </c>
+      <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>12</v>
+      </c>
+      <c r="B72" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s12-PAR</v>
+      </c>
+      <c r="C72" t="s">
+        <v>433</v>
+      </c>
+      <c r="D72" t="s">
+        <v>673</v>
+      </c>
+      <c r="E72" t="s">
+        <v>674</v>
+      </c>
+      <c r="F72" t="s">
+        <v>502</v>
+      </c>
+      <c r="G72" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>12</v>
+      </c>
+      <c r="B73" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s12-PAR</v>
+      </c>
+      <c r="C73" t="s">
+        <v>434</v>
+      </c>
+      <c r="D73" t="s">
+        <v>676</v>
+      </c>
+      <c r="E73" t="s">
+        <v>677</v>
+      </c>
+      <c r="F73" t="s">
+        <v>502</v>
+      </c>
+      <c r="G73" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>13</v>
+      </c>
+      <c r="B74" t="str">
+        <f>_xlfn.CONCAT("TO-s",A74,"-PAR")</f>
+        <v>TO-s13-PAR</v>
+      </c>
+      <c r="C74" t="s">
+        <v>430</v>
+      </c>
+      <c r="D74" t="s">
+        <v>679</v>
+      </c>
+      <c r="E74" t="s">
+        <v>680</v>
+      </c>
+      <c r="F74" t="s">
+        <v>681</v>
+      </c>
+      <c r="G74" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>13</v>
+      </c>
+      <c r="B75" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s13-PAR</v>
+      </c>
+      <c r="C75" t="s">
+        <v>424</v>
+      </c>
+      <c r="D75" t="s">
+        <v>683</v>
+      </c>
+      <c r="E75" t="s">
+        <v>684</v>
+      </c>
+      <c r="F75" t="s">
+        <v>685</v>
+      </c>
+      <c r="G75" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>13</v>
+      </c>
+      <c r="B76" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s13-PAR</v>
+      </c>
+      <c r="C76" t="s">
+        <v>431</v>
+      </c>
+      <c r="D76" t="s">
+        <v>687</v>
+      </c>
+      <c r="E76" t="s">
+        <v>688</v>
+      </c>
+      <c r="F76" t="s">
+        <v>689</v>
+      </c>
+      <c r="G76" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>13</v>
+      </c>
+      <c r="B77" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s13-PAR</v>
+      </c>
+      <c r="C77" t="s">
+        <v>432</v>
+      </c>
+      <c r="D77" t="s">
+        <v>691</v>
+      </c>
+      <c r="E77" t="s">
+        <v>692</v>
+      </c>
+      <c r="F77" t="s">
+        <v>470</v>
+      </c>
+      <c r="G77" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>13</v>
+      </c>
+      <c r="B78" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s13-PAR</v>
+      </c>
+      <c r="C78" t="s">
+        <v>433</v>
+      </c>
+      <c r="D78" t="s">
+        <v>694</v>
+      </c>
+      <c r="E78" t="s">
+        <v>695</v>
+      </c>
+      <c r="F78" t="s">
+        <v>696</v>
+      </c>
+      <c r="G78" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>13</v>
+      </c>
+      <c r="B79" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s13-PAR</v>
+      </c>
+      <c r="C79" t="s">
+        <v>434</v>
+      </c>
+      <c r="D79" t="s">
+        <v>697</v>
+      </c>
+      <c r="E79" t="s">
+        <v>698</v>
+      </c>
+      <c r="F79" t="s">
+        <v>438</v>
+      </c>
+      <c r="G79" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>14</v>
+      </c>
+      <c r="B80" t="str">
+        <f>_xlfn.CONCAT("TO-s",A80,"-PAR")</f>
+        <v>TO-s14-PAR</v>
+      </c>
+      <c r="C80" t="s">
+        <v>430</v>
+      </c>
+      <c r="D80" t="s">
+        <v>700</v>
+      </c>
+      <c r="E80" t="s">
+        <v>701</v>
+      </c>
+      <c r="F80" t="s">
+        <v>466</v>
+      </c>
+      <c r="G80" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>14</v>
+      </c>
+      <c r="B81" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s14-PAR</v>
+      </c>
+      <c r="C81" t="s">
+        <v>424</v>
+      </c>
+      <c r="D81" t="s">
+        <v>703</v>
+      </c>
+      <c r="E81" t="s">
+        <v>704</v>
+      </c>
+      <c r="F81" t="s">
+        <v>163</v>
+      </c>
+      <c r="G81" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>14</v>
+      </c>
+      <c r="B82" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s14-PAR</v>
+      </c>
+      <c r="C82" t="s">
+        <v>431</v>
+      </c>
+      <c r="D82" t="s">
+        <v>706</v>
+      </c>
+      <c r="E82" t="s">
+        <v>707</v>
+      </c>
+      <c r="F82" t="s">
+        <v>422</v>
+      </c>
+      <c r="G82" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>14</v>
+      </c>
+      <c r="B83" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s14-PAR</v>
+      </c>
+      <c r="C83" t="s">
+        <v>432</v>
+      </c>
+      <c r="D83" t="s">
+        <v>709</v>
+      </c>
+      <c r="E83" t="s">
+        <v>710</v>
+      </c>
+      <c r="F83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G83" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>14</v>
+      </c>
+      <c r="B84" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s14-PAR</v>
+      </c>
+      <c r="C84" t="s">
+        <v>433</v>
+      </c>
+      <c r="D84" t="s">
+        <v>712</v>
+      </c>
+      <c r="E84" t="s">
+        <v>713</v>
+      </c>
+      <c r="F84" t="s">
+        <v>714</v>
+      </c>
+      <c r="G84" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>14</v>
+      </c>
+      <c r="B85" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s14-PAR</v>
+      </c>
+      <c r="C85" t="s">
+        <v>434</v>
+      </c>
+      <c r="D85" t="s">
+        <v>716</v>
+      </c>
+      <c r="E85" t="s">
+        <v>717</v>
+      </c>
+      <c r="F85" t="s">
+        <v>718</v>
+      </c>
+      <c r="G85" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>15</v>
+      </c>
+      <c r="B86" t="str">
+        <f>_xlfn.CONCAT("TO-s",A86,"-PAR")</f>
+        <v>TO-s15-PAR</v>
+      </c>
+      <c r="C86" t="s">
+        <v>430</v>
+      </c>
+      <c r="D86" t="s">
+        <v>720</v>
+      </c>
+      <c r="E86" t="s">
+        <v>454</v>
+      </c>
+      <c r="F86" t="s">
+        <v>721</v>
+      </c>
+      <c r="G86" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>15</v>
+      </c>
+      <c r="B87" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s15-PAR</v>
+      </c>
+      <c r="C87" t="s">
+        <v>424</v>
+      </c>
+      <c r="D87" t="s">
+        <v>723</v>
+      </c>
+      <c r="E87" t="s">
+        <v>724</v>
+      </c>
+      <c r="F87" t="s">
+        <v>681</v>
+      </c>
+      <c r="G87" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>15</v>
+      </c>
+      <c r="B88" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s15-PAR</v>
+      </c>
+      <c r="C88" t="s">
+        <v>431</v>
+      </c>
+      <c r="D88" t="s">
+        <v>726</v>
+      </c>
+      <c r="E88" t="s">
+        <v>727</v>
+      </c>
+      <c r="F88" t="s">
+        <v>481</v>
+      </c>
+      <c r="G88" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>15</v>
+      </c>
+      <c r="B89" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s15-PAR</v>
+      </c>
+      <c r="C89" t="s">
+        <v>432</v>
+      </c>
+      <c r="D89" t="s">
+        <v>729</v>
+      </c>
+      <c r="E89" t="s">
+        <v>730</v>
+      </c>
+      <c r="F89" t="s">
+        <v>696</v>
+      </c>
+      <c r="G89" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>15</v>
+      </c>
+      <c r="B90" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s15-PAR</v>
+      </c>
+      <c r="C90" t="s">
+        <v>433</v>
+      </c>
+      <c r="D90" t="s">
+        <v>732</v>
+      </c>
+      <c r="E90" t="s">
+        <v>733</v>
+      </c>
+      <c r="F90" t="s">
+        <v>438</v>
+      </c>
+      <c r="G90" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>15</v>
+      </c>
+      <c r="B91" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s15-PAR</v>
+      </c>
+      <c r="C91" t="s">
+        <v>434</v>
+      </c>
+      <c r="D91" t="s">
+        <v>735</v>
+      </c>
+      <c r="E91" t="s">
+        <v>736</v>
+      </c>
+      <c r="F91" t="s">
+        <v>470</v>
+      </c>
+      <c r="G91" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>16</v>
+      </c>
+      <c r="B92" t="str">
+        <f>_xlfn.CONCAT("TO-s",A92,"-PAR")</f>
+        <v>TO-s16-PAR</v>
+      </c>
+      <c r="C92" t="s">
+        <v>430</v>
+      </c>
+      <c r="D92" t="s">
+        <v>738</v>
+      </c>
+      <c r="E92" t="s">
+        <v>739</v>
+      </c>
+      <c r="F92" t="s">
+        <v>681</v>
+      </c>
+      <c r="G92" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>16</v>
+      </c>
+      <c r="B93" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s16-PAR</v>
+      </c>
+      <c r="C93" t="s">
+        <v>424</v>
+      </c>
+      <c r="D93" t="s">
+        <v>741</v>
+      </c>
+      <c r="E93" t="s">
+        <v>742</v>
+      </c>
+      <c r="F93" t="s">
+        <v>175</v>
+      </c>
+      <c r="G93" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>16</v>
+      </c>
+      <c r="B94" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s16-PAR</v>
+      </c>
+      <c r="C94" t="s">
+        <v>431</v>
+      </c>
+      <c r="D94" t="s">
+        <v>744</v>
+      </c>
+      <c r="E94" t="s">
+        <v>745</v>
+      </c>
+      <c r="F94" t="s">
+        <v>291</v>
+      </c>
+      <c r="G94" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>16</v>
+      </c>
+      <c r="B95" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s16-PAR</v>
+      </c>
+      <c r="C95" t="s">
+        <v>432</v>
+      </c>
+      <c r="D95" t="s">
+        <v>746</v>
+      </c>
+      <c r="E95" t="s">
+        <v>747</v>
+      </c>
+      <c r="F95" t="s">
+        <v>481</v>
+      </c>
+      <c r="G95" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>16</v>
+      </c>
+      <c r="B96" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s16-PAR</v>
+      </c>
+      <c r="C96" t="s">
+        <v>433</v>
+      </c>
+      <c r="D96" t="s">
+        <v>749</v>
+      </c>
+      <c r="E96" t="s">
+        <v>750</v>
+      </c>
+      <c r="F96" t="s">
+        <v>512</v>
+      </c>
+      <c r="G96" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>16</v>
+      </c>
+      <c r="B97" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s16-PAR</v>
+      </c>
+      <c r="C97" t="s">
+        <v>434</v>
+      </c>
+      <c r="D97" t="s">
+        <v>752</v>
+      </c>
+      <c r="E97" t="s">
+        <v>753</v>
+      </c>
+      <c r="F97" t="s">
+        <v>530</v>
+      </c>
+      <c r="G97" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>17</v>
+      </c>
+      <c r="B98" t="str">
+        <f>_xlfn.CONCAT("TO-s",A98,"-PAR")</f>
+        <v>TO-s17-PAR</v>
+      </c>
+      <c r="C98" t="s">
+        <v>430</v>
+      </c>
+      <c r="D98" t="s">
+        <v>754</v>
+      </c>
+      <c r="E98" t="s">
+        <v>755</v>
+      </c>
+      <c r="F98" t="s">
+        <v>689</v>
+      </c>
+      <c r="G98" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>17</v>
+      </c>
+      <c r="B99" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s17-PAR</v>
+      </c>
+      <c r="C99" t="s">
+        <v>424</v>
+      </c>
+      <c r="D99" t="s">
+        <v>757</v>
+      </c>
+      <c r="E99" t="s">
+        <v>758</v>
+      </c>
+      <c r="F99" t="s">
+        <v>291</v>
+      </c>
+      <c r="G99" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>17</v>
+      </c>
+      <c r="B100" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s17-PAR</v>
+      </c>
+      <c r="C100" t="s">
+        <v>431</v>
+      </c>
+      <c r="D100" t="s">
+        <v>760</v>
+      </c>
+      <c r="E100" t="s">
+        <v>761</v>
+      </c>
+      <c r="F100" t="s">
+        <v>762</v>
+      </c>
+      <c r="G100" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>17</v>
+      </c>
+      <c r="B101" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s17-PAR</v>
+      </c>
+      <c r="C101" t="s">
+        <v>432</v>
+      </c>
+      <c r="D101" t="s">
+        <v>763</v>
+      </c>
+      <c r="E101" t="s">
+        <v>764</v>
+      </c>
+      <c r="F101" t="s">
+        <v>474</v>
+      </c>
+      <c r="G101" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>17</v>
+      </c>
+      <c r="B102" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s17-PAR</v>
+      </c>
+      <c r="C102" t="s">
+        <v>433</v>
+      </c>
+      <c r="D102" t="s">
+        <v>766</v>
+      </c>
+      <c r="E102" t="s">
+        <v>767</v>
+      </c>
+      <c r="F102" t="s">
+        <v>768</v>
+      </c>
+      <c r="G102" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>17</v>
+      </c>
+      <c r="B103" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s17-PAR</v>
+      </c>
+      <c r="C103" t="s">
+        <v>434</v>
+      </c>
+      <c r="D103" t="s">
+        <v>770</v>
+      </c>
+      <c r="E103" t="s">
+        <v>771</v>
+      </c>
+      <c r="F103" t="s">
+        <v>772</v>
+      </c>
+      <c r="G103" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>18</v>
+      </c>
+      <c r="B104" t="str">
+        <f>_xlfn.CONCAT("TO-s",A104,"-PAR")</f>
+        <v>TO-s18-PAR</v>
+      </c>
+      <c r="C104" t="s">
+        <v>430</v>
+      </c>
+      <c r="D104" t="s">
+        <v>774</v>
+      </c>
+      <c r="E104" t="s">
+        <v>775</v>
+      </c>
+      <c r="F104" t="s">
+        <v>537</v>
+      </c>
+      <c r="G104" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>18</v>
+      </c>
+      <c r="B105" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s18-PAR</v>
+      </c>
+      <c r="C105" t="s">
+        <v>424</v>
+      </c>
+      <c r="D105" t="s">
+        <v>776</v>
+      </c>
+      <c r="E105" t="s">
+        <v>777</v>
+      </c>
+      <c r="F105" t="s">
+        <v>778</v>
+      </c>
+      <c r="G105" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>18</v>
+      </c>
+      <c r="B106" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s18-PAR</v>
+      </c>
+      <c r="C106" t="s">
+        <v>431</v>
+      </c>
+      <c r="D106" t="s">
+        <v>780</v>
+      </c>
+      <c r="E106" t="s">
+        <v>781</v>
+      </c>
+      <c r="F106" t="s">
+        <v>446</v>
+      </c>
+      <c r="G106" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>18</v>
+      </c>
+      <c r="B107" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s18-PAR</v>
+      </c>
+      <c r="C107" t="s">
+        <v>432</v>
+      </c>
+      <c r="D107" t="s">
+        <v>782</v>
+      </c>
+      <c r="E107" t="s">
+        <v>783</v>
+      </c>
+      <c r="F107" t="s">
+        <v>784</v>
+      </c>
+      <c r="G107" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>18</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s18-PAR</v>
+      </c>
+      <c r="C108" t="s">
+        <v>433</v>
+      </c>
+      <c r="D108" t="s">
+        <v>786</v>
+      </c>
+      <c r="E108" t="s">
+        <v>787</v>
+      </c>
+      <c r="F108" t="s">
+        <v>772</v>
+      </c>
+      <c r="G108" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>18</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s18-PAR</v>
+      </c>
+      <c r="C109" t="s">
+        <v>434</v>
+      </c>
+      <c r="D109" t="s">
+        <v>789</v>
+      </c>
+      <c r="E109" t="s">
+        <v>790</v>
+      </c>
+      <c r="F109" t="s">
+        <v>466</v>
+      </c>
+      <c r="G109" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>19</v>
+      </c>
+      <c r="B110" t="str">
+        <f>_xlfn.CONCAT("TO-s",A110,"-PAR")</f>
+        <v>TO-s19-PAR</v>
+      </c>
+      <c r="C110" t="s">
+        <v>430</v>
+      </c>
+      <c r="D110" t="s">
+        <v>792</v>
+      </c>
+      <c r="E110" t="s">
+        <v>793</v>
+      </c>
+      <c r="F110" t="s">
+        <v>794</v>
+      </c>
+      <c r="G110" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>19</v>
+      </c>
+      <c r="B111" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s19-PAR</v>
+      </c>
+      <c r="C111" t="s">
+        <v>424</v>
+      </c>
+      <c r="D111" t="s">
+        <v>796</v>
+      </c>
+      <c r="E111" t="s">
+        <v>797</v>
+      </c>
+      <c r="F111" t="s">
+        <v>798</v>
+      </c>
+      <c r="G111" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>19</v>
+      </c>
+      <c r="B112" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s19-PAR</v>
+      </c>
+      <c r="C112" t="s">
+        <v>431</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>19</v>
+      </c>
+      <c r="B113" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s19-PAR</v>
+      </c>
+      <c r="C113" t="s">
+        <v>432</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>19</v>
+      </c>
+      <c r="B114" t="str">
+        <f t="shared" si="2"/>
+        <v>TO-s19-PAR</v>
+      </c>
+      <c r="C114" t="s">
+        <v>433</v>
+      </c>
+      <c r="D114" t="s">
+        <v>806</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>19</v>
+      </c>
+      <c r="B115" t="str">
+        <f t="shared" ref="B115" si="3">_xlfn.CONCAT("TO-s",A115,"-PAR")</f>
+        <v>TO-s19-PAR</v>
+      </c>
+      <c r="C115" t="s">
+        <v>434</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>20</v>
+      </c>
+      <c r="B116" t="str">
+        <f>_xlfn.CONCAT("TO-s",A116,"-PAR")</f>
+        <v>TO-s20-PAR</v>
+      </c>
+      <c r="C116" t="s">
+        <v>430</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>20</v>
+      </c>
+      <c r="B117" t="str">
+        <f t="shared" ref="B117:B121" si="4">_xlfn.CONCAT("TO-s",A117,"-PAR")</f>
+        <v>TO-s20-PAR</v>
+      </c>
+      <c r="C117" t="s">
+        <v>424</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>20</v>
+      </c>
+      <c r="B118" t="str">
+        <f t="shared" si="4"/>
+        <v>TO-s20-PAR</v>
+      </c>
+      <c r="C118" t="s">
+        <v>431</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>20</v>
+      </c>
+      <c r="B119" t="str">
+        <f t="shared" si="4"/>
+        <v>TO-s20-PAR</v>
+      </c>
+      <c r="C119" t="s">
+        <v>432</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>20</v>
+      </c>
+      <c r="B120" t="str">
+        <f t="shared" si="4"/>
+        <v>TO-s20-PAR</v>
+      </c>
+      <c r="C120" t="s">
+        <v>433</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>20</v>
+      </c>
+      <c r="B121" t="str">
+        <f t="shared" si="4"/>
+        <v>TO-s20-PAR</v>
+      </c>
+      <c r="C121" t="s">
+        <v>434</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>21</v>
+      </c>
+      <c r="B122" t="str">
+        <f>_xlfn.CONCAT("TO-s",A122,"-PAR")</f>
+        <v>TO-s21-PAR</v>
+      </c>
+      <c r="C122" t="s">
+        <v>430</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>21</v>
+      </c>
+      <c r="B123" t="str">
+        <f t="shared" ref="B123:B127" si="5">_xlfn.CONCAT("TO-s",A123,"-PAR")</f>
+        <v>TO-s21-PAR</v>
+      </c>
+      <c r="C123" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>21</v>
+      </c>
+      <c r="B124" t="str">
+        <f t="shared" si="5"/>
+        <v>TO-s21-PAR</v>
+      </c>
+      <c r="C124" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>21</v>
+      </c>
+      <c r="B125" t="str">
+        <f t="shared" si="5"/>
+        <v>TO-s21-PAR</v>
+      </c>
+      <c r="C125" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>21</v>
+      </c>
+      <c r="B126" t="str">
+        <f t="shared" si="5"/>
+        <v>TO-s21-PAR</v>
+      </c>
+      <c r="C126" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>21</v>
+      </c>
+      <c r="B127" t="str">
+        <f t="shared" si="5"/>
+        <v>TO-s21-PAR</v>
+      </c>
+      <c r="C127" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>22</v>
+      </c>
+      <c r="B128" t="str">
+        <f>_xlfn.CONCAT("TO-s",A128,"-PAR")</f>
+        <v>TO-s22-PAR</v>
+      </c>
+      <c r="C128" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>22</v>
+      </c>
+      <c r="B129" t="str">
+        <f t="shared" ref="B129:B133" si="6">_xlfn.CONCAT("TO-s",A129,"-PAR")</f>
+        <v>TO-s22-PAR</v>
+      </c>
+      <c r="C129" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>22</v>
+      </c>
+      <c r="B130" t="str">
+        <f t="shared" si="6"/>
+        <v>TO-s22-PAR</v>
+      </c>
+      <c r="C130" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>22</v>
+      </c>
+      <c r="B131" t="str">
+        <f t="shared" si="6"/>
+        <v>TO-s22-PAR</v>
+      </c>
+      <c r="C131" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>22</v>
+      </c>
+      <c r="B132" t="str">
+        <f t="shared" si="6"/>
+        <v>TO-s22-PAR</v>
+      </c>
+      <c r="C132" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>22</v>
+      </c>
+      <c r="B133" t="str">
+        <f t="shared" si="6"/>
+        <v>TO-s22-PAR</v>
+      </c>
+      <c r="C133" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>23</v>
+      </c>
+      <c r="B134" t="str">
+        <f>_xlfn.CONCAT("TO-s",A134,"-PAR")</f>
+        <v>TO-s23-PAR</v>
+      </c>
+      <c r="C134" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>23</v>
+      </c>
+      <c r="B135" t="str">
+        <f t="shared" ref="B135:B139" si="7">_xlfn.CONCAT("TO-s",A135,"-PAR")</f>
+        <v>TO-s23-PAR</v>
+      </c>
+      <c r="C135" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>23</v>
+      </c>
+      <c r="B136" t="str">
+        <f t="shared" si="7"/>
+        <v>TO-s23-PAR</v>
+      </c>
+      <c r="C136" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>23</v>
+      </c>
+      <c r="B137" t="str">
+        <f t="shared" si="7"/>
+        <v>TO-s23-PAR</v>
+      </c>
+      <c r="C137" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>23</v>
+      </c>
+      <c r="B138" t="str">
+        <f t="shared" si="7"/>
+        <v>TO-s23-PAR</v>
+      </c>
+      <c r="C138" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>23</v>
+      </c>
+      <c r="B139" t="str">
+        <f t="shared" si="7"/>
+        <v>TO-s23-PAR</v>
+      </c>
+      <c r="C139" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>24</v>
+      </c>
+      <c r="B140" t="str">
+        <f>_xlfn.CONCAT("TO-s",A140,"-PAR")</f>
+        <v>TO-s24-PAR</v>
+      </c>
+      <c r="C140" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>24</v>
+      </c>
+      <c r="B141" t="str">
+        <f t="shared" ref="B141:B145" si="8">_xlfn.CONCAT("TO-s",A141,"-PAR")</f>
+        <v>TO-s24-PAR</v>
+      </c>
+      <c r="C141" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>24</v>
+      </c>
+      <c r="B142" t="str">
+        <f t="shared" si="8"/>
+        <v>TO-s24-PAR</v>
+      </c>
+      <c r="C142" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>24</v>
+      </c>
+      <c r="B143" t="str">
+        <f t="shared" si="8"/>
+        <v>TO-s24-PAR</v>
+      </c>
+      <c r="C143" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>24</v>
+      </c>
+      <c r="B144" t="str">
+        <f t="shared" si="8"/>
+        <v>TO-s24-PAR</v>
+      </c>
+      <c r="C144" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>24</v>
+      </c>
+      <c r="B145" t="str">
+        <f t="shared" si="8"/>
+        <v>TO-s24-PAR</v>
+      </c>
+      <c r="C145" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>25</v>
+      </c>
+      <c r="B146" t="str">
+        <f>_xlfn.CONCAT("TO-s",A146,"-PAR")</f>
+        <v>TO-s25-PAR</v>
+      </c>
+      <c r="C146" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>25</v>
+      </c>
+      <c r="B147" t="str">
+        <f t="shared" ref="B147:B151" si="9">_xlfn.CONCAT("TO-s",A147,"-PAR")</f>
+        <v>TO-s25-PAR</v>
+      </c>
+      <c r="C147" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>25</v>
+      </c>
+      <c r="B148" t="str">
+        <f t="shared" si="9"/>
+        <v>TO-s25-PAR</v>
+      </c>
+      <c r="C148" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>25</v>
+      </c>
+      <c r="B149" t="str">
+        <f t="shared" si="9"/>
+        <v>TO-s25-PAR</v>
+      </c>
+      <c r="C149" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>25</v>
+      </c>
+      <c r="B150" t="str">
+        <f t="shared" si="9"/>
+        <v>TO-s25-PAR</v>
+      </c>
+      <c r="C150" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>25</v>
+      </c>
+      <c r="B151" t="str">
+        <f t="shared" si="9"/>
+        <v>TO-s25-PAR</v>
+      </c>
+      <c r="C151" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>26</v>
+      </c>
+      <c r="B152" t="str">
+        <f>_xlfn.CONCAT("TO-s",A152,"-PAR")</f>
+        <v>TO-s26-PAR</v>
+      </c>
+      <c r="C152" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>26</v>
+      </c>
+      <c r="B153" t="str">
+        <f t="shared" ref="B153:B157" si="10">_xlfn.CONCAT("TO-s",A153,"-PAR")</f>
+        <v>TO-s26-PAR</v>
+      </c>
+      <c r="C153" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>26</v>
+      </c>
+      <c r="B154" t="str">
+        <f t="shared" si="10"/>
+        <v>TO-s26-PAR</v>
+      </c>
+      <c r="C154" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>26</v>
+      </c>
+      <c r="B155" t="str">
+        <f t="shared" si="10"/>
+        <v>TO-s26-PAR</v>
+      </c>
+      <c r="C155" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>26</v>
+      </c>
+      <c r="B156" t="str">
+        <f t="shared" si="10"/>
+        <v>TO-s26-PAR</v>
+      </c>
+      <c r="C156" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>26</v>
+      </c>
+      <c r="B157" t="str">
+        <f t="shared" si="10"/>
+        <v>TO-s26-PAR</v>
+      </c>
+      <c r="C157" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>27</v>
+      </c>
+      <c r="B158" t="str">
+        <f>_xlfn.CONCAT("TO-s",A158,"-PAR")</f>
+        <v>TO-s27-PAR</v>
+      </c>
+      <c r="C158" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>27</v>
+      </c>
+      <c r="B159" t="str">
+        <f t="shared" ref="B159:B163" si="11">_xlfn.CONCAT("TO-s",A159,"-PAR")</f>
+        <v>TO-s27-PAR</v>
+      </c>
+      <c r="C159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>27</v>
+      </c>
+      <c r="B160" t="str">
+        <f t="shared" si="11"/>
+        <v>TO-s27-PAR</v>
+      </c>
+      <c r="C160" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>27</v>
+      </c>
+      <c r="B161" t="str">
+        <f t="shared" si="11"/>
+        <v>TO-s27-PAR</v>
+      </c>
+      <c r="C161" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>27</v>
+      </c>
+      <c r="B162" t="str">
+        <f t="shared" si="11"/>
+        <v>TO-s27-PAR</v>
+      </c>
+      <c r="C162" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>27</v>
+      </c>
+      <c r="B163" t="str">
+        <f t="shared" si="11"/>
+        <v>TO-s27-PAR</v>
+      </c>
+      <c r="C163" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>28</v>
+      </c>
+      <c r="B164" t="str">
+        <f>_xlfn.CONCAT("TO-s",A164,"-PAR")</f>
+        <v>TO-s28-PAR</v>
+      </c>
+      <c r="C164" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>28</v>
+      </c>
+      <c r="B165" t="str">
+        <f t="shared" ref="B165:B169" si="12">_xlfn.CONCAT("TO-s",A165,"-PAR")</f>
+        <v>TO-s28-PAR</v>
+      </c>
+      <c r="C165" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>28</v>
+      </c>
+      <c r="B166" t="str">
+        <f t="shared" si="12"/>
+        <v>TO-s28-PAR</v>
+      </c>
+      <c r="C166" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>28</v>
+      </c>
+      <c r="B167" t="str">
+        <f t="shared" si="12"/>
+        <v>TO-s28-PAR</v>
+      </c>
+      <c r="C167" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>28</v>
+      </c>
+      <c r="B168" t="str">
+        <f t="shared" si="12"/>
+        <v>TO-s28-PAR</v>
+      </c>
+      <c r="C168" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>28</v>
+      </c>
+      <c r="B169" t="str">
+        <f t="shared" si="12"/>
+        <v>TO-s28-PAR</v>
+      </c>
+      <c r="C169" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>29</v>
+      </c>
+      <c r="B170" t="str">
+        <f>_xlfn.CONCAT("TO-s",A170,"-PAR")</f>
+        <v>TO-s29-PAR</v>
+      </c>
+      <c r="C170" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>29</v>
+      </c>
+      <c r="B171" t="str">
+        <f t="shared" ref="B171:B175" si="13">_xlfn.CONCAT("TO-s",A171,"-PAR")</f>
+        <v>TO-s29-PAR</v>
+      </c>
+      <c r="C171" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>29</v>
+      </c>
+      <c r="B172" t="str">
+        <f t="shared" si="13"/>
+        <v>TO-s29-PAR</v>
+      </c>
+      <c r="C172" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>29</v>
+      </c>
+      <c r="B173" t="str">
+        <f t="shared" si="13"/>
+        <v>TO-s29-PAR</v>
+      </c>
+      <c r="C173" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>29</v>
+      </c>
+      <c r="B174" t="str">
+        <f t="shared" si="13"/>
+        <v>TO-s29-PAR</v>
+      </c>
+      <c r="C174" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>29</v>
+      </c>
+      <c r="B175" t="str">
+        <f t="shared" si="13"/>
+        <v>TO-s29-PAR</v>
+      </c>
+      <c r="C175" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>30</v>
+      </c>
+      <c r="B176" t="str">
+        <f>_xlfn.CONCAT("TO-s",A176,"-PAR")</f>
+        <v>TO-s30-PAR</v>
+      </c>
+      <c r="C176" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>30</v>
+      </c>
+      <c r="B177" t="str">
+        <f t="shared" ref="B177:B181" si="14">_xlfn.CONCAT("TO-s",A177,"-PAR")</f>
+        <v>TO-s30-PAR</v>
+      </c>
+      <c r="C177" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>30</v>
+      </c>
+      <c r="B178" t="str">
+        <f t="shared" si="14"/>
+        <v>TO-s30-PAR</v>
+      </c>
+      <c r="C178" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>30</v>
+      </c>
+      <c r="B179" t="str">
+        <f t="shared" si="14"/>
+        <v>TO-s30-PAR</v>
+      </c>
+      <c r="C179" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>30</v>
+      </c>
+      <c r="B180" t="str">
+        <f t="shared" si="14"/>
+        <v>TO-s30-PAR</v>
+      </c>
+      <c r="C180" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>30</v>
+      </c>
+      <c r="B181" t="str">
+        <f t="shared" si="14"/>
+        <v>TO-s30-PAR</v>
+      </c>
+      <c r="C181" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>31</v>
+      </c>
+      <c r="B182" t="str">
+        <f>_xlfn.CONCAT("TO-s",A182,"-PAR")</f>
+        <v>TO-s31-PAR</v>
+      </c>
+      <c r="C182" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>31</v>
+      </c>
+      <c r="B183" t="str">
+        <f t="shared" ref="B183:B187" si="15">_xlfn.CONCAT("TO-s",A183,"-PAR")</f>
+        <v>TO-s31-PAR</v>
+      </c>
+      <c r="C183" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>31</v>
+      </c>
+      <c r="B184" t="str">
+        <f t="shared" si="15"/>
+        <v>TO-s31-PAR</v>
+      </c>
+      <c r="C184" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>31</v>
+      </c>
+      <c r="B185" t="str">
+        <f t="shared" si="15"/>
+        <v>TO-s31-PAR</v>
+      </c>
+      <c r="C185" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>31</v>
+      </c>
+      <c r="B186" t="str">
+        <f t="shared" si="15"/>
+        <v>TO-s31-PAR</v>
+      </c>
+      <c r="C186" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>31</v>
+      </c>
+      <c r="B187" t="str">
+        <f t="shared" si="15"/>
+        <v>TO-s31-PAR</v>
+      </c>
+      <c r="C187" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>32</v>
+      </c>
+      <c r="B188" t="str">
+        <f>_xlfn.CONCAT("TO-s",A188,"-PAR")</f>
+        <v>TO-s32-PAR</v>
+      </c>
+      <c r="C188" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>32</v>
+      </c>
+      <c r="B189" t="str">
+        <f t="shared" ref="B189:B193" si="16">_xlfn.CONCAT("TO-s",A189,"-PAR")</f>
+        <v>TO-s32-PAR</v>
+      </c>
+      <c r="C189" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>32</v>
+      </c>
+      <c r="B190" t="str">
+        <f t="shared" si="16"/>
+        <v>TO-s32-PAR</v>
+      </c>
+      <c r="C190" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>32</v>
+      </c>
+      <c r="B191" t="str">
+        <f t="shared" si="16"/>
+        <v>TO-s32-PAR</v>
+      </c>
+      <c r="C191" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>32</v>
+      </c>
+      <c r="B192" t="str">
+        <f t="shared" si="16"/>
+        <v>TO-s32-PAR</v>
+      </c>
+      <c r="C192" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>32</v>
+      </c>
+      <c r="B193" t="str">
+        <f t="shared" si="16"/>
+        <v>TO-s32-PAR</v>
+      </c>
+      <c r="C193" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>33</v>
+      </c>
+      <c r="B194" t="str">
+        <f>_xlfn.CONCAT("TO-s",A194,"-PAR")</f>
+        <v>TO-s33-PAR</v>
+      </c>
+      <c r="C194" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>33</v>
+      </c>
+      <c r="B195" t="str">
+        <f t="shared" ref="B195:B199" si="17">_xlfn.CONCAT("TO-s",A195,"-PAR")</f>
+        <v>TO-s33-PAR</v>
+      </c>
+      <c r="C195" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>33</v>
+      </c>
+      <c r="B196" t="str">
+        <f t="shared" si="17"/>
+        <v>TO-s33-PAR</v>
+      </c>
+      <c r="C196" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>33</v>
+      </c>
+      <c r="B197" t="str">
+        <f t="shared" si="17"/>
+        <v>TO-s33-PAR</v>
+      </c>
+      <c r="C197" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>33</v>
+      </c>
+      <c r="B198" t="str">
+        <f t="shared" si="17"/>
+        <v>TO-s33-PAR</v>
+      </c>
+      <c r="C198" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>33</v>
+      </c>
+      <c r="B199" t="str">
+        <f t="shared" si="17"/>
+        <v>TO-s33-PAR</v>
+      </c>
+      <c r="C199" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>34</v>
+      </c>
+      <c r="B200" t="str">
+        <f>_xlfn.CONCAT("TO-s",A200,"-PAR")</f>
+        <v>TO-s34-PAR</v>
+      </c>
+      <c r="C200" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <v>34</v>
+      </c>
+      <c r="B201" t="str">
+        <f t="shared" ref="B201:B205" si="18">_xlfn.CONCAT("TO-s",A201,"-PAR")</f>
+        <v>TO-s34-PAR</v>
+      </c>
+      <c r="C201" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202">
+        <v>34</v>
+      </c>
+      <c r="B202" t="str">
+        <f t="shared" si="18"/>
+        <v>TO-s34-PAR</v>
+      </c>
+      <c r="C202" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <v>34</v>
+      </c>
+      <c r="B203" t="str">
+        <f t="shared" si="18"/>
+        <v>TO-s34-PAR</v>
+      </c>
+      <c r="C203" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <v>34</v>
+      </c>
+      <c r="B204" t="str">
+        <f t="shared" si="18"/>
+        <v>TO-s34-PAR</v>
+      </c>
+      <c r="C204" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <v>34</v>
+      </c>
+      <c r="B205" t="str">
+        <f t="shared" si="18"/>
+        <v>TO-s34-PAR</v>
+      </c>
+      <c r="C205" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D122" r:id="rId1" xr:uid="{2674AFF8-3EE6-404D-9DAC-B7E8C9F38E0E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/doc/calendario.xlsx
+++ b/src/doc/calendario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773F9EF7-4A5A-4F22-A19C-80F25613F71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849F3B2C-4703-4CBB-B031-88E89FCFE3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="1480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="1480">
   <si>
     <t>Domingo 1º de Adviento</t>
   </si>
@@ -19579,7 +19579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0EFA39-5D96-4259-A1EE-44E9BC9B401F}">
-  <dimension ref="A8:V72"/>
+  <dimension ref="A8:V80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
@@ -19595,7 +19595,7 @@
         <v>1476</v>
       </c>
       <c r="C8" s="6" t="str">
-        <f t="shared" ref="C8:C11" si="0">_xlfn.CONCAT("// TIEMPO ORDINARIO - SEMANA ",A8," ",B8)</f>
+        <f t="shared" ref="C8:C10" si="0">_xlfn.CONCAT("// TIEMPO ORDINARIO - SEMANA ",A8," ",B8)</f>
         <v>// TIEMPO ORDINARIO - SEMANA 34 LUNES</v>
       </c>
     </row>
@@ -19702,27 +19702,27 @@
     </row>
     <row r="16" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
         <v>1476</v>
       </c>
       <c r="C16" s="6" t="str">
         <f>_xlfn.CONCAT("// TIEMPO DE CUARESMA - SEMANA ",A16," ",B16)</f>
-        <v>// TIEMPO DE CUARESMA - SEMANA 6 LUNES</v>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 LUNES</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>A16</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B17" t="s">
         <v>1477</v>
       </c>
       <c r="C17" s="6" t="str">
         <f t="shared" ref="C17:C21" si="5">_xlfn.CONCAT("// TIEMPO DE CUARESMA - SEMANA ",A17," ",B17)</f>
-        <v>// TIEMPO DE CUARESMA - SEMANA 6 MARTES</v>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 MARTES</v>
       </c>
       <c r="M17">
         <v>456.43</v>
@@ -19738,14 +19738,14 @@
     <row r="18" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" ref="A18:A21" si="6">A17</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
         <v>1475</v>
       </c>
       <c r="C18" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>// TIEMPO DE CUARESMA - SEMANA 6 MIERCOLES</v>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 MIERCOLES</v>
       </c>
       <c r="M18">
         <f>+O18/N18</f>
@@ -19761,14 +19761,14 @@
     <row r="19" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
         <v>1472</v>
       </c>
       <c r="C19" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>// TIEMPO DE CUARESMA - SEMANA 6 JUEVES</v>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 JUEVES</v>
       </c>
       <c r="M19">
         <f>+M17-M18</f>
@@ -19782,27 +19782,27 @@
     <row r="20" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
         <v>1473</v>
       </c>
       <c r="C20" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>// TIEMPO DE CUARESMA - SEMANA 6 VIERNES</v>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 VIERNES</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
         <v>1474</v>
       </c>
       <c r="C21" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>// TIEMPO DE CUARESMA - SEMANA 6 SABADO</v>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 SABADO</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
@@ -19829,13 +19829,13 @@
         <v>1479</v>
       </c>
       <c r="C26" s="6" t="str">
-        <f t="shared" ref="C26:C72" si="8">_xlfn.CONCAT("// TIEMPO ORDINARIO - SEMANA ",A26," ",B26)</f>
+        <f t="shared" ref="C26:C58" si="8">_xlfn.CONCAT("// TIEMPO ORDINARIO - SEMANA ",A26," ",B26)</f>
         <v>// TIEMPO ORDINARIO - SEMANA 2 DOMINGO</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" ref="A27:A59" si="9">+A26+1</f>
+        <f t="shared" ref="A27:A58" si="9">+A26+1</f>
         <v>3</v>
       </c>
       <c r="B27" t="s">
@@ -20418,6 +20418,83 @@
       <c r="C72" s="6" t="str">
         <f t="shared" si="10"/>
         <v>// TIEMPO ADVIENTO - SEMANA 13 DOMINGO</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C75" s="6" t="str">
+        <f>_xlfn.CONCAT("// TIEMPO DE CUARESMA - SEMANA ",A75," ",B75)</f>
+        <v>// TIEMPO DE CUARESMA - SEMANA 1 DOMINGO</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <f>+A75+1</f>
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C76" s="6" t="str">
+        <f>_xlfn.CONCAT("// TIEMPO DE CUARESMA - SEMANA ",A76," ",B76)</f>
+        <v>// TIEMPO DE CUARESMA - SEMANA 2 DOMINGO</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <f t="shared" ref="A77:A80" si="12">+A76+1</f>
+        <v>3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C77" s="6" t="str">
+        <f t="shared" ref="C77:C80" si="13">_xlfn.CONCAT("// TIEMPO DE CUARESMA - SEMANA ",A77," ",B77)</f>
+        <v>// TIEMPO DE CUARESMA - SEMANA 3 DOMINGO</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C78" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>// TIEMPO DE CUARESMA - SEMANA 4 DOMINGO</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C79" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>// TIEMPO DE CUARESMA - SEMANA 5 DOMINGO</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C80" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>// TIEMPO DE CUARESMA - SEMANA 6 DOMINGO</v>
       </c>
     </row>
   </sheetData>

--- a/src/doc/calendario.xlsx
+++ b/src/doc/calendario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849F3B2C-4703-4CBB-B031-88E89FCFE3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E5A9EE-973A-410F-82CF-51E192C11CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="1480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3495" uniqueCount="1485">
   <si>
     <t>Domingo 1º de Adviento</t>
   </si>
@@ -4517,6 +4517,21 @@
   <si>
     <t>DOMINGO</t>
   </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>Isaías 2, 1-5 / Isaías 4, 2-6</t>
+  </si>
+  <si>
+    <t>Mateo 8, 5-11</t>
+  </si>
+  <si>
+    <t>Sal 79, 4</t>
+  </si>
 </sst>
 </file>
 
@@ -4525,7 +4540,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4579,6 +4594,19 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -4628,7 +4656,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -4645,6 +4673,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -7285,7 +7318,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AFBACE-E0D0-47E0-A7DB-4F0CC57B5A5B}">
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:J415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -19009,7 +19042,7 @@
         <v>968</v>
       </c>
       <c r="D391" t="str">
-        <f t="shared" ref="D391:D409" si="9">_xlfn.CONCAT(A391,"-s",B391,"-",C391)</f>
+        <f t="shared" ref="D391:D415" si="9">_xlfn.CONCAT(A391,"-s",B391,"-",C391)</f>
         <v>TO-s31-IMP</v>
       </c>
       <c r="E391" t="s">
@@ -19566,6 +19599,126 @@
       </c>
       <c r="I409" t="s">
         <v>1170</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B410">
+        <v>1</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D410" t="str">
+        <f t="shared" si="9"/>
+        <v>CU-s1-abc</v>
+      </c>
+      <c r="E410" t="s">
+        <v>430</v>
+      </c>
+      <c r="F410" s="10" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G410" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H410" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="I410" s="11" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B411">
+        <v>1</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D411" t="str">
+        <f t="shared" si="9"/>
+        <v>CU-s1-abc</v>
+      </c>
+      <c r="E411" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B412">
+        <v>1</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D412" t="str">
+        <f t="shared" si="9"/>
+        <v>CU-s1-abc</v>
+      </c>
+      <c r="E412" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B413">
+        <v>1</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D413" t="str">
+        <f t="shared" si="9"/>
+        <v>CU-s1-abc</v>
+      </c>
+      <c r="E413" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B414">
+        <v>1</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D414" t="str">
+        <f t="shared" si="9"/>
+        <v>CU-s1-abc</v>
+      </c>
+      <c r="E414" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B415">
+        <v>1</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D415" t="str">
+        <f t="shared" si="9"/>
+        <v>CU-s1-abc</v>
+      </c>
+      <c r="E415" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>

--- a/src/doc/calendario.xlsx
+++ b/src/doc/calendario.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E5A9EE-973A-410F-82CF-51E192C11CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791C7C02-8FE2-4B53-9EDE-F85571F409F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{50C77ACD-27A8-4560-9522-4B1F3607ED08}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3495" uniqueCount="1485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="1494">
   <si>
     <t>Domingo 1º de Adviento</t>
   </si>
@@ -4531,6 +4532,33 @@
   </si>
   <si>
     <t>Sal 79, 4</t>
+  </si>
+  <si>
+    <t>scorazondeJesus</t>
+  </si>
+  <si>
+    <t>Sagrado corazón de Jesus</t>
+  </si>
+  <si>
+    <t>Adviento</t>
+  </si>
+  <si>
+    <t>L/S</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>ener 1-12</t>
+  </si>
+  <si>
+    <t>dic 17-31</t>
+  </si>
+  <si>
+    <t>Navidad</t>
+  </si>
+  <si>
+    <t>Misa (Vigilia, Medianoche, Aurora, Día)</t>
   </si>
 </sst>
 </file>
@@ -4656,7 +4684,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -4678,6 +4706,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -5014,6 +5043,88 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67E4A3A-44F4-41F8-B1CA-180F19C99737}">
+  <dimension ref="B3:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10C50CC-0950-4C80-A067-6CCB3F4EAE54}">
   <dimension ref="A1:L114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7316,7 +7427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AFBACE-E0D0-47E0-A7DB-4F0CC57B5A5B}">
   <dimension ref="A1:J415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19730,7 +19841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0EFA39-5D96-4259-A1EE-44E9BC9B401F}">
   <dimension ref="A8:V80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
